--- a/UI_Software_Project_Initiation_and_Planning/cash-flow-maui.xlsx
+++ b/UI_Software_Project_Initiation_and_Planning/cash-flow-maui.xlsx
@@ -18,80 +18,80 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={882d51af-3269-1bf7-4b31-3a1fe6104ee7}</author>
-    <author>tc={f371b72e-01bb-4eff-94b7-498a70678990}</author>
-    <author>tc={f7502d59-83b0-d240-5c48-7c39ef60fd2b}</author>
-    <author>tc={1b68213d-f6f6-f657-fa35-a6d00303f1e9}</author>
-    <author>tc={634663f2-d2b3-3a7d-3e3b-991cb0d723cc}</author>
-    <author>tc={301ab3af-bfe9-fbaa-859d-261c589fa9f2}</author>
-    <author>tc={4f2a1241-44bf-d498-0ea2-c11a8d4815f4}</author>
-    <author>tc={b9bd068f-f1c0-5629-2808-14d6a02e9dba}</author>
-    <author>tc={9f58acf7-774a-dbb2-4396-b55c51337c6a}</author>
-    <author>tc={ff35b7df-1374-6ae7-2864-78e270dde45f}</author>
-    <author>tc={9239f211-c845-074f-71ae-15b52f4914af}</author>
-    <author>tc={3ae576e4-ca1e-55a3-ec97-b3162a9c0046}</author>
-    <author>tc={ca82f6b1-ebfe-bcc6-0ad2-abf9eed412a1}</author>
-    <author>tc={0d7b761e-67cd-d103-48b9-6ba9fa5b3974}</author>
-    <author>tc={fbb78e0e-b469-79dc-21c9-b1051b3ca13e}</author>
-    <author>tc={3182d2cf-055a-7452-681f-336e0cf3edd5}</author>
-    <author>tc={e5990929-1305-2dbe-2b28-4c8ac32f72e7}</author>
-    <author>tc={38cf6407-3771-fb48-8e62-9033830e9cdb}</author>
-    <author>tc={5caf605a-ebb2-9c14-fb1e-835ef20c1bf4}</author>
-    <author>tc={1559d2dc-baa2-d59f-9ff9-099eafa1bce2}</author>
-    <author>tc={62661412-6e4d-5f67-cfcb-58834a1f4a39}</author>
-    <author>tc={5afdfb06-e9b9-ab1c-97bd-9e698185e3d1}</author>
-    <author>tc={1a016af7-264a-8326-9d49-8d2a0adfbead}</author>
-    <author>tc={446e22c4-2eda-d01d-32c0-5bf5e2063d70}</author>
-    <author>tc={ae850658-0f17-3c29-d172-e8afe9b4837e}</author>
-    <author>tc={73265cac-29c5-69dd-3c45-0292a3a478ce}</author>
-    <author>tc={ac3d8698-9b3d-e95e-ea6c-134758a61ed8}</author>
-    <author>tc={1637cc03-32bd-a4be-7eea-98b3d3b9235f}</author>
-    <author>tc={aaed5316-baa9-6a6d-4652-32c815638106}</author>
-    <author>tc={5855cac1-58d0-ab89-3415-d090ad9d2ba4}</author>
-    <author>tc={f01c77f3-bede-b77e-7b53-84a0a9f23036}</author>
-    <author>tc={2ed74b0b-3d71-2cc8-626d-b729ca96166b}</author>
-    <author>tc={8417ebe6-7ea4-4304-6f96-e87b7b4e0b43}</author>
-    <author>tc={53ff781a-2a83-ceb6-a0a7-06f3fc9e3ffd}</author>
-    <author>tc={f5220219-14c2-7a7f-380e-14538249b9ab}</author>
-    <author>tc={3aeab38a-d7b4-e210-e230-cfab656d48bc}</author>
-    <author>tc={5b2d23fe-34dc-be59-9656-f43d8adc2074}</author>
-    <author>tc={6df50f23-655e-5df7-16ad-befdd0bc96e1}</author>
-    <author>tc={ae2bba9e-dc11-722d-c83a-2b12b5c4f6a8}</author>
-    <author>tc={c51ffbb3-ee99-6a9b-f5f0-d0917c62837a}</author>
-    <author>tc={e1dcf7b9-90b3-b661-1de8-3b67359c5c7d}</author>
-    <author>tc={df1bac1b-7e7f-abcb-a67c-0d1077507e9d}</author>
-    <author>tc={2e42492d-90b7-6953-d2d3-8319d4a91e88}</author>
-    <author>tc={104227df-22ef-c507-2eb9-53fac1bc6b74}</author>
-    <author>tc={a6932d2a-b3dd-d894-6c88-b67b25f9cf9a}</author>
-    <author>tc={6809d84c-d9c6-40b0-67fb-05262d615d77}</author>
-    <author>tc={3bb02673-9ce8-c793-0c70-61be9881bcdf}</author>
-    <author>tc={abaebfe0-7556-6190-cf03-a4b8ea0839b7}</author>
-    <author>tc={a2bdd411-2cbf-30eb-a448-a0dd5b228658}</author>
-    <author>tc={9c7d0011-60bd-79df-8a1a-91403ef77edc}</author>
-    <author>tc={5210a8ae-646e-e94a-4779-985a3280ac02}</author>
-    <author>tc={b4026a48-5250-6578-aa06-07446ec6894c}</author>
-    <author>tc={35fc713c-c9c5-c0a5-a9a4-9b7a6d70bfc5}</author>
-    <author>tc={72b4233f-9e08-bb03-b475-099470f1e367}</author>
-    <author>tc={0e8e5db2-bb19-7969-3f4f-949488887d52}</author>
-    <author>tc={bcd66f2e-18c5-8f5e-e055-aa7f412fb090}</author>
-    <author>tc={7f51f8d1-c8f0-a84d-f9a8-74a8b5aa15c3}</author>
-    <author>tc={79bf3859-14e7-106a-bacb-6b94fe278f8b}</author>
-    <author>tc={b5f35f55-2424-b548-b367-622dcf753a3e}</author>
-    <author>tc={9d66f356-3ca5-c191-8a99-35a53de775ec}</author>
-    <author>tc={baa9df04-efd9-7be4-c5c9-2b1a18f98aae}</author>
-    <author>tc={f6502e8f-2091-03e3-6e3b-d3ee4ee2b584}</author>
-    <author>tc={20ea3103-cf0f-3469-a596-ee8da6370d8c}</author>
-    <author>tc={d895b3cd-2bcd-1ed4-1036-eaaca1b3783d}</author>
-    <author>tc={6324958d-5d3f-fae7-c89f-3fc4bbc1ffda}</author>
-    <author>tc={c52f62ad-2dd7-aec6-0e55-80e9af53b1f9}</author>
-    <author>tc={d428a997-f208-389a-09cd-7381a0844d47}</author>
-    <author>tc={770b60d9-d001-5d79-1b4d-a6f623dcd238}</author>
-    <author>tc={05a2c7ac-cc92-dbe1-c98b-9e0ad6f89599}</author>
-    <author>tc={46c23f41-f179-4967-070f-530d995ea988}</author>
-    <author>tc={f0e94bc5-6fe1-2ab8-14f8-d84e8a63ff88}</author>
+    <author>tc={882D51AF-3269-1BF7-4B31-3A1FE6104EE7}</author>
+    <author>tc={F371B72E-01BB-4EFF-94B7-498A70678990}</author>
+    <author>tc={F7502D59-83B0-D240-5C48-7C39EF60FD2B}</author>
+    <author>tc={1B68213D-F6F6-F657-FA35-A6D00303F1E9}</author>
+    <author>tc={634663F2-D2B3-3A7D-3E3B-991CB0D723CC}</author>
+    <author>tc={301AB3AF-BFE9-FBAA-859D-261C589FA9F2}</author>
+    <author>tc={4F2A1241-44BF-D498-0EA2-C11A8D4815F4}</author>
+    <author>tc={B9BD068F-F1C0-5629-2808-14D6A02E9DBA}</author>
+    <author>tc={9F58ACF7-774A-DBB2-4396-B55C51337C6A}</author>
+    <author>tc={FF35B7DF-1374-6AE7-2864-78E270DDE45F}</author>
+    <author>tc={9239F211-C845-074F-71AE-15B52F4914AF}</author>
+    <author>tc={3AE576E4-CA1E-55A3-EC97-B3162A9C0046}</author>
+    <author>tc={CA82F6B1-EBFE-BCC6-0AD2-ABF9EED412A1}</author>
+    <author>tc={0D7B761E-67CD-D103-48B9-6BA9FA5B3974}</author>
+    <author>tc={FBB78E0E-B469-79DC-21C9-B1051B3CA13E}</author>
+    <author>tc={3182D2CF-055A-7452-681F-336E0CF3EDD5}</author>
+    <author>tc={E5990929-1305-2DBE-2B28-4C8AC32F72E7}</author>
+    <author>tc={38CF6407-3771-FB48-8E62-9033830E9CDB}</author>
+    <author>tc={5CAF605A-EBB2-9C14-FB1E-835EF20C1BF4}</author>
+    <author>tc={1559D2DC-BAA2-D59F-9FF9-099EAFA1BCE2}</author>
+    <author>tc={62661412-6E4D-5F67-CFCB-58834A1F4A39}</author>
+    <author>tc={5AFDFB06-E9B9-AB1C-97BD-9E698185E3D1}</author>
+    <author>tc={1A016AF7-264A-8326-9D49-8D2A0ADFBEAD}</author>
+    <author>tc={446E22C4-2EDA-D01D-32C0-5BF5E2063D70}</author>
+    <author>tc={AE850658-0F17-3C29-D172-E8AFE9B4837E}</author>
+    <author>tc={73265CAC-29C5-69DD-3C45-0292A3A478CE}</author>
+    <author>tc={AC3D8698-9B3D-E95E-EA6C-134758A61ED8}</author>
+    <author>tc={1637CC03-32BD-A4BE-7EEA-98B3D3B9235F}</author>
+    <author>tc={AAED5316-BAA9-6A6D-4652-32C815638106}</author>
+    <author>tc={5855CAC1-58D0-AB89-3415-D090AD9D2BA4}</author>
+    <author>tc={F01C77F3-BEDE-B77E-7B53-84A0A9F23036}</author>
+    <author>tc={2ED74B0B-3D71-2CC8-626D-B729CA96166B}</author>
+    <author>tc={8417EBE6-7EA4-4304-6F96-E87B7B4E0B43}</author>
+    <author>tc={53FF781A-2A83-CEB6-A0A7-06F3FC9E3FFD}</author>
+    <author>tc={F5220219-14C2-7A7F-380E-14538249B9AB}</author>
+    <author>tc={3AEAB38A-D7B4-E210-E230-CFAB656D48BC}</author>
+    <author>tc={5B2D23FE-34DC-BE59-9656-F43D8ADC2074}</author>
+    <author>tc={6DF50F23-655E-5DF7-16AD-BEFDD0BC96E1}</author>
+    <author>tc={AE2BBA9E-DC11-722D-C83A-2B12B5C4F6A8}</author>
+    <author>tc={C51FFBB3-EE99-6A9B-F5F0-D0917C62837A}</author>
+    <author>tc={E1DCF7B9-90B3-B661-1DE8-3B67359C5C7D}</author>
+    <author>tc={DF1BAC1B-7E7F-ABCB-A67C-0D1077507E9D}</author>
+    <author>tc={2E42492D-90B7-6953-D2D3-8319D4A91E88}</author>
+    <author>tc={104227DF-22EF-C507-2EB9-53FAC1BC6B74}</author>
+    <author>tc={A6932D2A-B3DD-D894-6C88-B67B25F9CF9A}</author>
+    <author>tc={6809D84C-D9C6-40B0-67FB-05262D615D77}</author>
+    <author>tc={3BB02673-9CE8-C793-0C70-61BE9881BCDF}</author>
+    <author>tc={ABAEBFE0-7556-6190-CF03-A4B8EA0839B7}</author>
+    <author>tc={A2BDD411-2CBF-30EB-A448-A0DD5B228658}</author>
+    <author>tc={9C7D0011-60BD-79DF-8A1A-91403EF77EDC}</author>
+    <author>tc={5210A8AE-646E-E94A-4779-985A3280AC02}</author>
+    <author>tc={B4026A48-5250-6578-AA06-07446EC6894C}</author>
+    <author>tc={35FC713C-C9C5-C0A5-A9A4-9B7A6D70BFC5}</author>
+    <author>tc={72B4233F-9E08-BB03-B475-099470F1E367}</author>
+    <author>tc={0E8E5DB2-BB19-7969-3F4F-949488887D52}</author>
+    <author>tc={BCD66F2E-18C5-8F5E-E055-AA7F412FB090}</author>
+    <author>tc={7F51F8D1-C8F0-A84D-F9A8-74A8B5AA15C3}</author>
+    <author>tc={79BF3859-14E7-106A-BACB-6B94FE278F8B}</author>
+    <author>tc={B5F35F55-2424-B548-B367-622DCF753A3E}</author>
+    <author>tc={9D66F356-3CA5-C191-8A99-35A53DE775EC}</author>
+    <author>tc={BAA9DF04-EFD9-7BE4-C5C9-2B1A18F98AAE}</author>
+    <author>tc={F6502E8F-2091-03E3-6E3B-D3EE4EE2B584}</author>
+    <author>tc={20EA3103-CF0F-3469-A596-EE8DA6370D8C}</author>
+    <author>tc={D895B3CD-2BCD-1ED4-1036-EAACA1B3783D}</author>
+    <author>tc={6324958D-5D3F-FAE7-C89F-3FC4BBC1FFDA}</author>
+    <author>tc={C52F62AD-2DD7-AEC6-0E55-80E9AF53B1F9}</author>
+    <author>tc={D428A997-F208-389A-09CD-7381A0844D47}</author>
+    <author>tc={770B60D9-D001-5D79-1B4D-A6F623DCD238}</author>
+    <author>tc={05A2C7AC-CC92-DBE1-C98B-9E0AD6F89599}</author>
+    <author>tc={46C23F41-F179-4967-070F-530D995EA988}</author>
+    <author>tc={F0E94BC5-6FE1-2AB8-14F8-D84E8A63FF88}</author>
   </authors>
   <commentList>
-    <comment ref="A21" authorId="0" xr:uid="{882d51af-3269-1bf7-4b31-3a1fe6104ee7}">
+    <comment ref="A21" authorId="0" xr:uid="{882D51AF-3269-1BF7-4B31-3A1FE6104EE7}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={008C007E-0023-4F06-A3B3-004C00380013}:</t>
         </r>
         <r>
           <rPr>
@@ -114,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A23" authorId="1" xr:uid="{f371b72e-01bb-4eff-94b7-498a70678990}">
+    <comment ref="A23" authorId="1" xr:uid="{F371B72E-01BB-4EFF-94B7-498A70678990}">
       <text>
         <r>
           <rPr>
@@ -122,7 +122,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={000A0034-008D-4F81-B648-007800350074}:</t>
         </r>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="2" xr:uid="{f7502d59-83b0-d240-5c48-7c39ef60fd2b}">
+    <comment ref="B23" authorId="2" xr:uid="{F7502D59-83B0-D240-5C48-7C39EF60FD2B}">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00410082-006F-446F-AB02-00A900AB0075}:</t>
         </r>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P23" authorId="3" xr:uid="{1b68213d-f6f6-f657-fa35-a6d00303f1e9}">
+    <comment ref="P23" authorId="3" xr:uid="{1B68213D-F6F6-F657-FA35-A6D00303F1E9}">
       <text>
         <r>
           <rPr>
@@ -167,7 +167,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={002900DC-007D-4F15-904A-00E600880094}:</t>
         </r>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="4" xr:uid="{634663f2-d2b3-3a7d-3e3b-991cb0d723cc}">
+    <comment ref="C23" authorId="4" xr:uid="{634663F2-D2B3-3A7D-3E3B-991CB0D723CC}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00AF0088-00C3-44F0-9579-00E800BB008E}:</t>
         </r>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A24" authorId="5" xr:uid="{301ab3af-bfe9-fbaa-859d-261c589fa9f2}">
+    <comment ref="A24" authorId="5" xr:uid="{301AB3AF-BFE9-FBAA-859D-261C589FA9F2}">
       <text>
         <r>
           <rPr>
@@ -211,7 +211,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00540021-003C-492A-B2FD-005F00F90049}:</t>
         </r>
         <r>
           <rPr>
@@ -226,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K24" authorId="6" xr:uid="{4f2a1241-44bf-d498-0ea2-c11a8d4815f4}">
+    <comment ref="K24" authorId="6" xr:uid="{4F2A1241-44BF-D498-0EA2-C11A8D4815F4}">
       <text>
         <r>
           <rPr>
@@ -234,7 +234,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0059000A-00A0-4A23-A0BD-00C300BE0010}:</t>
         </r>
         <r>
           <rPr>
@@ -248,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L24" authorId="7" xr:uid="{b9bd068f-f1c0-5629-2808-14d6a02e9dba}">
+    <comment ref="L24" authorId="7" xr:uid="{B9BD068F-F1C0-5629-2808-14D6A02E9DBA}">
       <text>
         <r>
           <rPr>
@@ -256,7 +256,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={008E0068-0086-408D-AF6C-008A00FB0035}:</t>
         </r>
         <r>
           <rPr>
@@ -270,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M24" authorId="8" xr:uid="{9f58acf7-774a-dbb2-4396-b55c51337c6a}">
+    <comment ref="M24" authorId="8" xr:uid="{9F58ACF7-774A-DBB2-4396-B55C51337C6A}">
       <text>
         <r>
           <rPr>
@@ -278,7 +278,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00A40077-0088-470B-9B0A-003D00D5002C}:</t>
         </r>
         <r>
           <rPr>
@@ -292,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N24" authorId="9" xr:uid="{ff35b7df-1374-6ae7-2864-78e270dde45f}">
+    <comment ref="N24" authorId="9" xr:uid="{FF35B7DF-1374-6AE7-2864-78E270DDE45F}">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00900010-00DE-49B2-85BB-00FC00C300A3}:</t>
         </r>
         <r>
           <rPr>
@@ -314,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O24" authorId="10" xr:uid="{9239f211-c845-074f-71ae-15b52f4914af}">
+    <comment ref="O24" authorId="10" xr:uid="{9239F211-C845-074F-71AE-15B52F4914AF}">
       <text>
         <r>
           <rPr>
@@ -322,7 +322,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00CA00DF-0022-42D1-ACE6-0078005D003D}:</t>
         </r>
         <r>
           <rPr>
@@ -336,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="11" xr:uid="{3ae576e4-ca1e-55a3-ec97-b3162a9c0046}">
+    <comment ref="D24" authorId="11" xr:uid="{3AE576E4-CA1E-55A3-EC97-B3162A9C0046}">
       <text>
         <r>
           <rPr>
@@ -344,7 +344,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00D000E8-00D5-4F68-97B4-007A00E1000F}:</t>
         </r>
         <r>
           <rPr>
@@ -358,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="12" xr:uid="{ca82f6b1-ebfe-bcc6-0ad2-abf9eed412a1}">
+    <comment ref="G24" authorId="12" xr:uid="{CA82F6B1-EBFE-BCC6-0AD2-ABF9EED412A1}">
       <text>
         <r>
           <rPr>
@@ -366,7 +366,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00A100FD-00DA-43A9-9597-005C00B10024}:</t>
         </r>
         <r>
           <rPr>
@@ -380,7 +380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="13" xr:uid="{0d7b761e-67cd-d103-48b9-6ba9fa5b3974}">
+    <comment ref="H24" authorId="13" xr:uid="{0D7B761E-67CD-D103-48B9-6BA9FA5B3974}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00430049-00F8-4F7E-8CBF-008D00D300FA}:</t>
         </r>
         <r>
           <rPr>
@@ -402,7 +402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="14" xr:uid="{fbb78e0e-b469-79dc-21c9-b1051b3ca13e}">
+    <comment ref="I24" authorId="14" xr:uid="{FBB78E0E-B469-79DC-21C9-B1051B3CA13E}">
       <text>
         <r>
           <rPr>
@@ -410,7 +410,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003D00C9-005D-4302-98A2-001100700003}:</t>
         </r>
         <r>
           <rPr>
@@ -424,7 +424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="15" xr:uid="{3182d2cf-055a-7452-681f-336e0cf3edd5}">
+    <comment ref="J24" authorId="15" xr:uid="{3182D2CF-055A-7452-681F-336E0CF3EDD5}">
       <text>
         <r>
           <rPr>
@@ -432,7 +432,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={001400D8-0082-4168-89A2-00DC004C0084}:</t>
         </r>
         <r>
           <rPr>
@@ -446,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A26" authorId="16" xr:uid="{e5990929-1305-2dbe-2b28-4c8ac32f72e7}">
+    <comment ref="A26" authorId="16" xr:uid="{E5990929-1305-2DBE-2B28-4C8AC32F72E7}">
       <text>
         <r>
           <rPr>
@@ -454,7 +454,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={001D00CE-0016-4306-B87C-00FF00550024}:</t>
         </r>
         <r>
           <rPr>
@@ -468,7 +468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A27" authorId="17" xr:uid="{38cf6407-3771-fb48-8e62-9033830e9cdb}">
+    <comment ref="A27" authorId="17" xr:uid="{38CF6407-3771-FB48-8E62-9033830E9CDB}">
       <text>
         <r>
           <rPr>
@@ -476,7 +476,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00F4007C-0098-4D8E-8DCC-000200750039}:</t>
         </r>
         <r>
           <rPr>
@@ -492,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A28" authorId="18" xr:uid="{5caf605a-ebb2-9c14-fb1e-835ef20c1bf4}">
+    <comment ref="A28" authorId="18" xr:uid="{5CAF605A-EBB2-9C14-FB1E-835EF20C1BF4}">
       <text>
         <r>
           <rPr>
@@ -500,7 +500,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00D5004E-003A-4E51-AAD5-00D900650090}:</t>
         </r>
         <r>
           <rPr>
@@ -515,7 +515,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A29" authorId="19" xr:uid="{1559d2dc-baa2-d59f-9ff9-099eafa1bce2}">
+    <comment ref="A29" authorId="19" xr:uid="{1559D2DC-BAA2-D59F-9FF9-099EAFA1BCE2}">
       <text>
         <r>
           <rPr>
@@ -523,7 +523,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={005A0090-00B9-433D-B11B-00D600DF006A}:</t>
         </r>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A30" authorId="20" xr:uid="{62661412-6e4d-5f67-cfcb-58834a1f4a39}">
+    <comment ref="A30" authorId="20" xr:uid="{62661412-6E4D-5F67-CFCB-58834A1F4A39}">
       <text>
         <r>
           <rPr>
@@ -546,7 +546,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={001F00E3-00B3-40F1-BFEC-00620040007D}:</t>
         </r>
         <r>
           <rPr>
@@ -561,7 +561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A31" authorId="21" xr:uid="{5afdfb06-e9b9-ab1c-97bd-9e698185e3d1}">
+    <comment ref="A31" authorId="21" xr:uid="{5AFDFB06-E9B9-AB1C-97BD-9E698185E3D1}">
       <text>
         <r>
           <rPr>
@@ -569,7 +569,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={004400BD-002C-4741-B2D4-0078000A0074}:</t>
         </r>
         <r>
           <rPr>
@@ -584,7 +584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A32" authorId="22" xr:uid="{1a016af7-264a-8326-9d49-8d2a0adfbead}">
+    <comment ref="A32" authorId="22" xr:uid="{1A016AF7-264A-8326-9D49-8D2A0ADFBEAD}">
       <text>
         <r>
           <rPr>
@@ -592,7 +592,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00EF00E6-000B-45B5-B026-00260062006D}:</t>
         </r>
         <r>
           <rPr>
@@ -607,7 +607,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A33" authorId="23" xr:uid="{446e22c4-2eda-d01d-32c0-5bf5e2063d70}">
+    <comment ref="A33" authorId="23" xr:uid="{446E22C4-2EDA-D01D-32C0-5BF5E2063D70}">
       <text>
         <r>
           <rPr>
@@ -615,7 +615,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00C800FB-009E-400A-8779-000F0092007A}:</t>
         </r>
         <r>
           <rPr>
@@ -630,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="24" xr:uid="{ae850658-0f17-3c29-d172-e8afe9b4837e}">
+    <comment ref="A34" authorId="24" xr:uid="{AE850658-0F17-3C29-D172-E8AFE9B4837E}">
       <text>
         <r>
           <rPr>
@@ -638,7 +638,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={007B00EF-0012-42B0-A029-00EC00880021}:</t>
         </r>
         <r>
           <rPr>
@@ -653,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A35" authorId="25" xr:uid="{73265cac-29c5-69dd-3c45-0292a3a478ce}">
+    <comment ref="A35" authorId="25" xr:uid="{73265CAC-29C5-69DD-3C45-0292A3A478CE}">
       <text>
         <r>
           <rPr>
@@ -661,7 +661,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003A0085-00FC-474A-B7D2-0006005600DC}:</t>
         </r>
         <r>
           <rPr>
@@ -675,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A39" authorId="26" xr:uid="{ac3d8698-9b3d-e95e-ea6c-134758a61ed8}">
+    <comment ref="A39" authorId="26" xr:uid="{AC3D8698-9B3D-E95E-EA6C-134758A61ED8}">
       <text>
         <r>
           <rPr>
@@ -683,7 +683,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003900D8-00D3-4931-B0DA-00BD00B0009A}:</t>
         </r>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B39" authorId="27" xr:uid="{1637cc03-32bd-a4be-7eea-98b3d3b9235f}">
+    <comment ref="B39" authorId="27" xr:uid="{1637CC03-32BD-A4BE-7EEA-98B3D3B9235F}">
       <text>
         <r>
           <rPr>
@@ -707,7 +707,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00DC00BA-009D-45CB-8F5C-00E200170018}:</t>
         </r>
         <r>
           <rPr>
@@ -721,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P39" authorId="28" xr:uid="{aaed5316-baa9-6a6d-4652-32c815638106}">
+    <comment ref="P39" authorId="28" xr:uid="{AAED5316-BAA9-6A6D-4652-32C815638106}">
       <text>
         <r>
           <rPr>
@@ -729,7 +729,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003000D4-0074-49F1-B0E3-00040071003C}:</t>
         </r>
         <r>
           <rPr>
@@ -743,7 +743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C39" authorId="29" xr:uid="{5855cac1-58d0-ab89-3415-d090ad9d2ba4}">
+    <comment ref="C39" authorId="29" xr:uid="{5855CAC1-58D0-AB89-3415-D090AD9D2BA4}">
       <text>
         <r>
           <rPr>
@@ -751,7 +751,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={007E009F-0072-4832-93F2-00F30042007A}:</t>
         </r>
         <r>
           <rPr>
@@ -765,7 +765,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A40" authorId="30" xr:uid="{f01c77f3-bede-b77e-7b53-84a0a9f23036}">
+    <comment ref="A40" authorId="30" xr:uid="{F01C77F3-BEDE-B77E-7B53-84A0A9F23036}">
       <text>
         <r>
           <rPr>
@@ -773,7 +773,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={005A00ED-00FB-404E-8518-00E60039001E}:</t>
         </r>
         <r>
           <rPr>
@@ -788,7 +788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K40" authorId="31" xr:uid="{2ed74b0b-3d71-2cc8-626d-b729ca96166b}">
+    <comment ref="K40" authorId="31" xr:uid="{2ED74B0B-3D71-2CC8-626D-B729CA96166B}">
       <text>
         <r>
           <rPr>
@@ -796,7 +796,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00E8000B-00BA-4BCA-87AE-008F00D3006B}:</t>
         </r>
         <r>
           <rPr>
@@ -810,7 +810,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L40" authorId="32" xr:uid="{8417ebe6-7ea4-4304-6f96-e87b7b4e0b43}">
+    <comment ref="L40" authorId="32" xr:uid="{8417EBE6-7EA4-4304-6F96-E87B7B4E0B43}">
       <text>
         <r>
           <rPr>
@@ -818,7 +818,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00B700D2-00F4-487F-825A-008900B60054}:</t>
         </r>
         <r>
           <rPr>
@@ -832,7 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M40" authorId="33" xr:uid="{53ff781a-2a83-ceb6-a0a7-06f3fc9e3ffd}">
+    <comment ref="M40" authorId="33" xr:uid="{53FF781A-2A83-CEB6-A0A7-06F3FC9E3FFD}">
       <text>
         <r>
           <rPr>
@@ -840,7 +840,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00FB00ED-00E9-4692-8907-00E800E30001}:</t>
         </r>
         <r>
           <rPr>
@@ -854,7 +854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N40" authorId="34" xr:uid="{f5220219-14c2-7a7f-380e-14538249b9ab}">
+    <comment ref="N40" authorId="34" xr:uid="{F5220219-14C2-7A7F-380E-14538249B9AB}">
       <text>
         <r>
           <rPr>
@@ -862,7 +862,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={008C00EB-0093-4B2F-A57D-0041005400F3}:</t>
         </r>
         <r>
           <rPr>
@@ -876,7 +876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O40" authorId="35" xr:uid="{3aeab38a-d7b4-e210-e230-cfab656d48bc}">
+    <comment ref="O40" authorId="35" xr:uid="{3AEAB38A-D7B4-E210-E230-CFAB656D48BC}">
       <text>
         <r>
           <rPr>
@@ -884,7 +884,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={004700AB-00D3-4A36-8747-003A00A60021}:</t>
         </r>
         <r>
           <rPr>
@@ -898,7 +898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D40" authorId="36" xr:uid="{5b2d23fe-34dc-be59-9656-f43d8adc2074}">
+    <comment ref="D40" authorId="36" xr:uid="{5B2D23FE-34DC-BE59-9656-F43D8ADC2074}">
       <text>
         <r>
           <rPr>
@@ -906,7 +906,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={008D00E5-00EC-4ABC-8233-000E009B0075}:</t>
         </r>
         <r>
           <rPr>
@@ -920,7 +920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E40" authorId="37" xr:uid="{6df50f23-655e-5df7-16ad-befdd0bc96e1}">
+    <comment ref="E40" authorId="37" xr:uid="{6DF50F23-655E-5DF7-16AD-BEFDD0BC96E1}">
       <text>
         <r>
           <rPr>
@@ -928,7 +928,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00C300A0-0006-4B87-9CD2-000D0098004C}:</t>
         </r>
         <r>
           <rPr>
@@ -942,7 +942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F40" authorId="38" xr:uid="{ae2bba9e-dc11-722d-c83a-2b12b5c4f6a8}">
+    <comment ref="F40" authorId="38" xr:uid="{AE2BBA9E-DC11-722D-C83A-2B12B5C4F6A8}">
       <text>
         <r>
           <rPr>
@@ -950,7 +950,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00D000B9-00AC-4796-AEFE-0019002800F9}:</t>
         </r>
         <r>
           <rPr>
@@ -964,7 +964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G40" authorId="39" xr:uid="{c51ffbb3-ee99-6a9b-f5f0-d0917c62837a}">
+    <comment ref="G40" authorId="39" xr:uid="{C51FFBB3-EE99-6A9B-F5F0-D0917C62837A}">
       <text>
         <r>
           <rPr>
@@ -972,7 +972,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00A20063-004F-4A97-904E-002A00770042}:</t>
         </r>
         <r>
           <rPr>
@@ -986,7 +986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H40" authorId="40" xr:uid="{e1dcf7b9-90b3-b661-1de8-3b67359c5c7d}">
+    <comment ref="H40" authorId="40" xr:uid="{E1DCF7B9-90B3-B661-1DE8-3B67359C5C7D}">
       <text>
         <r>
           <rPr>
@@ -994,7 +994,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00AA00A1-00C1-456E-96A5-00CB00D700E2}:</t>
         </r>
         <r>
           <rPr>
@@ -1008,7 +1008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I40" authorId="41" xr:uid="{df1bac1b-7e7f-abcb-a67c-0d1077507e9d}">
+    <comment ref="I40" authorId="41" xr:uid="{DF1BAC1B-7E7F-ABCB-A67C-0D1077507E9D}">
       <text>
         <r>
           <rPr>
@@ -1016,7 +1016,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={005B00CD-00BA-42B5-A4A0-009B003F0006}:</t>
         </r>
         <r>
           <rPr>
@@ -1030,7 +1030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J40" authorId="42" xr:uid="{2e42492d-90b7-6953-d2d3-8319d4a91e88}">
+    <comment ref="J40" authorId="42" xr:uid="{2E42492D-90B7-6953-D2D3-8319D4A91E88}">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1038,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003900E1-00A3-457B-8682-00FD006500B7}:</t>
         </r>
         <r>
           <rPr>
@@ -1052,7 +1052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A41" authorId="43" xr:uid="{104227df-22ef-c507-2eb9-53fac1bc6b74}">
+    <comment ref="A41" authorId="43" xr:uid="{104227DF-22EF-C507-2EB9-53FAC1BC6B74}">
       <text>
         <r>
           <rPr>
@@ -1060,7 +1060,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00AE0015-0057-4B36-882A-00CD00C700D0}:</t>
         </r>
         <r>
           <rPr>
@@ -1075,7 +1075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C41" authorId="44" xr:uid="{a6932d2a-b3dd-d894-6c88-b67b25f9cf9a}">
+    <comment ref="C41" authorId="44" xr:uid="{A6932D2A-B3DD-D894-6C88-B67B25F9CF9A}">
       <text>
         <r>
           <rPr>
@@ -1083,7 +1083,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00A100F9-0096-4A73-A8ED-00A8002D00D7}:</t>
         </r>
         <r>
           <rPr>
@@ -1097,7 +1097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A42" authorId="45" xr:uid="{6809d84c-d9c6-40b0-67fb-05262d615d77}">
+    <comment ref="A42" authorId="45" xr:uid="{6809D84C-D9C6-40B0-67FB-05262D615D77}">
       <text>
         <r>
           <rPr>
@@ -1105,7 +1105,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00B300CE-00DB-431F-86D6-0008005400A4}:</t>
         </r>
         <r>
           <rPr>
@@ -1119,7 +1119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A43" authorId="46" xr:uid="{3bb02673-9ce8-c793-0c70-61be9881bcdf}">
+    <comment ref="A43" authorId="46" xr:uid="{3BB02673-9CE8-C793-0C70-61BE9881BCDF}">
       <text>
         <r>
           <rPr>
@@ -1127,7 +1127,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={006A003E-006E-43A3-8898-00DB00C00037}:</t>
         </r>
         <r>
           <rPr>
@@ -1142,7 +1142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A44" authorId="47" xr:uid="{abaebfe0-7556-6190-cf03-a4b8ea0839b7}">
+    <comment ref="A44" authorId="47" xr:uid="{ABAEBFE0-7556-6190-CF03-A4B8EA0839B7}">
       <text>
         <r>
           <rPr>
@@ -1150,7 +1150,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00CE00C5-00FA-4A9A-9A2C-00A5001B0080}:</t>
         </r>
         <r>
           <rPr>
@@ -1166,7 +1166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A45" authorId="48" xr:uid="{a2bdd411-2cbf-30eb-a448-a0dd5b228658}">
+    <comment ref="A45" authorId="48" xr:uid="{A2BDD411-2CBF-30EB-A448-A0DD5B228658}">
       <text>
         <r>
           <rPr>
@@ -1174,7 +1174,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00EB0035-0010-4B54-9B49-00FC00B200E7}:</t>
         </r>
         <r>
           <rPr>
@@ -1189,7 +1189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A46" authorId="49" xr:uid="{9c7d0011-60bd-79df-8a1a-91403ef77edc}">
+    <comment ref="A46" authorId="49" xr:uid="{9C7D0011-60BD-79DF-8A1A-91403EF77EDC}">
       <text>
         <r>
           <rPr>
@@ -1197,7 +1197,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00530034-00A2-4256-9DF1-000D00F800C4}:</t>
         </r>
         <r>
           <rPr>
@@ -1212,7 +1212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A47" authorId="50" xr:uid="{5210a8ae-646e-e94a-4779-985a3280ac02}">
+    <comment ref="A47" authorId="50" xr:uid="{5210A8AE-646E-E94A-4779-985A3280AC02}">
       <text>
         <r>
           <rPr>
@@ -1220,7 +1220,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={009900B9-0088-49D9-B4E4-0015000300E7}:</t>
         </r>
         <r>
           <rPr>
@@ -1234,7 +1234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A48" authorId="51" xr:uid="{b4026a48-5250-6578-aa06-07446ec6894c}">
+    <comment ref="A48" authorId="51" xr:uid="{B4026A48-5250-6578-AA06-07446EC6894C}">
       <text>
         <r>
           <rPr>
@@ -1242,7 +1242,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00D70092-00FF-4E47-9229-00E8000A0012}:</t>
         </r>
         <r>
           <rPr>
@@ -1256,7 +1256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A49" authorId="52" xr:uid="{35fc713c-c9c5-c0a5-a9a4-9b7a6d70bfc5}">
+    <comment ref="A49" authorId="52" xr:uid="{35FC713C-C9C5-C0A5-A9A4-9B7A6D70BFC5}">
       <text>
         <r>
           <rPr>
@@ -1264,7 +1264,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={002900E1-0025-42C1-B58D-006E00ED007A}:</t>
         </r>
         <r>
           <rPr>
@@ -1278,7 +1278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A50" authorId="53" xr:uid="{72b4233f-9e08-bb03-b475-099470f1e367}">
+    <comment ref="A50" authorId="53" xr:uid="{72B4233F-9E08-BB03-B475-099470F1E367}">
       <text>
         <r>
           <rPr>
@@ -1286,7 +1286,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0030009A-007E-459C-AB1B-002100AD004A}:</t>
         </r>
         <r>
           <rPr>
@@ -1300,7 +1300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="54" xr:uid="{0e8e5db2-bb19-7969-3f4f-949488887d52}">
+    <comment ref="A51" authorId="54" xr:uid="{0E8E5DB2-BB19-7969-3F4F-949488887D52}">
       <text>
         <r>
           <rPr>
@@ -1308,7 +1308,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00900007-0072-44DF-99A9-009100EF001F}:</t>
         </r>
         <r>
           <rPr>
@@ -1322,7 +1322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A52" authorId="55" xr:uid="{bcd66f2e-18c5-8f5e-e055-aa7f412fb090}">
+    <comment ref="A52" authorId="55" xr:uid="{BCD66F2E-18C5-8F5E-E055-AA7F412FB090}">
       <text>
         <r>
           <rPr>
@@ -1330,7 +1330,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00720044-00CC-42C7-A14B-00E0007E008D}:</t>
         </r>
         <r>
           <rPr>
@@ -1345,7 +1345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A53" authorId="56" xr:uid="{7f51f8d1-c8f0-a84d-f9a8-74a8b5aa15c3}">
+    <comment ref="A53" authorId="56" xr:uid="{7F51F8D1-C8F0-A84D-F9A8-74A8B5AA15C3}">
       <text>
         <r>
           <rPr>
@@ -1353,7 +1353,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={000200C3-003D-4A43-89DE-004600C60098}:</t>
         </r>
         <r>
           <rPr>
@@ -1370,7 +1370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="57" xr:uid="{79bf3859-14e7-106a-bacb-6b94fe278f8b}">
+    <comment ref="D53" authorId="57" xr:uid="{79BF3859-14E7-106A-BACB-6B94FE278F8B}">
       <text>
         <r>
           <rPr>
@@ -1378,7 +1378,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00F200C9-00D7-4378-817E-008D005A003C}:</t>
         </r>
         <r>
           <rPr>
@@ -1395,7 +1395,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A54" authorId="58" xr:uid="{b5f35f55-2424-b548-b367-622dcf753a3e}">
+    <comment ref="A54" authorId="58" xr:uid="{B5F35F55-2424-B548-B367-622DCF753A3E}">
       <text>
         <r>
           <rPr>
@@ -1403,7 +1403,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00F600F0-0092-483E-AB11-0096006E00E6}:</t>
         </r>
         <r>
           <rPr>
@@ -1418,7 +1418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A55" authorId="59" xr:uid="{9d66f356-3ca5-c191-8a99-35a53de775ec}">
+    <comment ref="A55" authorId="59" xr:uid="{9D66F356-3CA5-C191-8A99-35A53DE775EC}">
       <text>
         <r>
           <rPr>
@@ -1426,7 +1426,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={004600A3-00CB-48A0-BCBA-00D3005E00F9}:</t>
         </r>
         <r>
           <rPr>
@@ -1440,7 +1440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A56" authorId="60" xr:uid="{baa9df04-efd9-7be4-c5c9-2b1a18f98aae}">
+    <comment ref="A56" authorId="60" xr:uid="{BAA9DF04-EFD9-7BE4-C5C9-2B1A18F98AAE}">
       <text>
         <r>
           <rPr>
@@ -1448,7 +1448,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={001F00A5-00C0-4F61-AE66-00CB0025004A}:</t>
         </r>
         <r>
           <rPr>
@@ -1462,7 +1462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A58" authorId="61" xr:uid="{f6502e8f-2091-03e3-6e3b-d3ee4ee2b584}">
+    <comment ref="A58" authorId="61" xr:uid="{F6502E8F-2091-03E3-6E3B-D3EE4EE2B584}">
       <text>
         <r>
           <rPr>
@@ -1470,7 +1470,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0042008A-0015-4672-B844-009A00E700A4}:</t>
         </r>
         <r>
           <rPr>
@@ -1485,7 +1485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A59" authorId="62" xr:uid="{20ea3103-cf0f-3469-a596-ee8da6370d8c}">
+    <comment ref="A59" authorId="62" xr:uid="{20EA3103-CF0F-3469-A596-EE8DA6370D8C}">
       <text>
         <r>
           <rPr>
@@ -1493,7 +1493,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0073003B-0052-4B7D-A143-006D00680045}:</t>
         </r>
         <r>
           <rPr>
@@ -1508,7 +1508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A60" authorId="63" xr:uid="{d895b3cd-2bcd-1ed4-1036-eaaca1b3783d}">
+    <comment ref="A60" authorId="63" xr:uid="{D895B3CD-2BCD-1ED4-1036-EAACA1B3783D}">
       <text>
         <r>
           <rPr>
@@ -1516,7 +1516,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00FC0076-0062-445D-9D9E-000A0092005F}:</t>
         </r>
         <r>
           <rPr>
@@ -1531,7 +1531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A61" authorId="64" xr:uid="{6324958d-5d3f-fae7-c89f-3fc4bbc1ffda}">
+    <comment ref="A61" authorId="64" xr:uid="{6324958D-5D3F-FAE7-C89F-3FC4BBC1FFDA}">
       <text>
         <r>
           <rPr>
@@ -1539,7 +1539,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0027004D-0016-43A3-BD4E-004600F20097}:</t>
         </r>
         <r>
           <rPr>
@@ -1554,7 +1554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A62" authorId="65" xr:uid="{c52f62ad-2dd7-aec6-0e55-80e9af53b1f9}">
+    <comment ref="A62" authorId="65" xr:uid="{C52F62AD-2DD7-AEC6-0E55-80E9AF53B1F9}">
       <text>
         <r>
           <rPr>
@@ -1562,7 +1562,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00C800A3-00A0-4D12-AA90-008D003B0089}:</t>
         </r>
         <r>
           <rPr>
@@ -1577,7 +1577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A63" authorId="66" xr:uid="{d428a997-f208-389a-09cd-7381a0844d47}">
+    <comment ref="A63" authorId="66" xr:uid="{D428A997-F208-389A-09CD-7381A0844D47}">
       <text>
         <r>
           <rPr>
@@ -1585,7 +1585,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00B100B2-0019-4A24-B868-005F00C30043}:</t>
         </r>
         <r>
           <rPr>
@@ -1599,7 +1599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B65" authorId="67" xr:uid="{770b60d9-d001-5d79-1b4d-a6f623dcd238}">
+    <comment ref="B65" authorId="67" xr:uid="{770B60D9-D001-5D79-1B4D-A6F623DCD238}">
       <text>
         <r>
           <rPr>
@@ -1607,7 +1607,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={003B0087-00FB-4E83-811E-00CD000100C6}:</t>
         </r>
         <r>
           <rPr>
@@ -1621,7 +1621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B67" authorId="68" xr:uid="{05a2c7ac-cc92-dbe1-c98b-9e0ad6f89599}">
+    <comment ref="B67" authorId="68" xr:uid="{05A2C7AC-CC92-DBE1-C98B-9E0AD6F89599}">
       <text>
         <r>
           <rPr>
@@ -1629,7 +1629,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={00C30083-00A7-4C91-94BB-00FF00150088}:</t>
         </r>
         <r>
           <rPr>
@@ -1643,7 +1643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B69" authorId="69" xr:uid="{46c23f41-f179-4967-070f-530d995ea988}">
+    <comment ref="B69" authorId="69" xr:uid="{46C23F41-F179-4967-070F-530D995EA988}">
       <text>
         <r>
           <rPr>
@@ -1651,7 +1651,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={002B00DC-00E0-49E1-B78E-00B1004000F4}:</t>
         </r>
         <r>
           <rPr>
@@ -1666,7 +1666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="70" xr:uid="{f0e94bc5-6fe1-2ab8-14f8-d84e8a63ff88}">
+    <comment ref="B76" authorId="70" xr:uid="{F0E94BC5-6FE1-2AB8-14F8-D84E8A63FF88}">
       <text>
         <r>
           <rPr>
@@ -1674,7 +1674,7 @@
             <sz val="9"/>
             <rFont val="Tahoma"/>
           </rPr>
-          <t>Comment:</t>
+          <t>tc={0055001B-004E-43BB-B0A8-00B2006800E8}:</t>
         </r>
         <r>
           <rPr>
@@ -1694,7 +1694,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">12-Month Cash Flow Forecast</t>
   </si>
@@ -1705,32 +1705,7 @@
     <t xml:space="preserve">Company Name:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Your Cash Flow Forecast (CFF) is an estimate of the money you expect to bring in to and pay out of your business over the next 12-months. Importantly, it should reflect all of the activity you have described in your Business Plan.  
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF002060"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> - Your CFF should show BUSINESS revenue and expenses only, not personal items;
- - Your CFF is FORWARD looking, reflecting future anticipated transactions into and out of your business;
- - You can input your loan amount and the term length (12-60months), which will autocalculate onto the CFF below;											
- - You will be asked to choose a start month for your CFF; this should be the next month after you expect to receive the loan and should match up with the month you selected in your Sales Assumptions;
- - Remember, some of the information that you have created in your Sales Assumptions will auto-populate in your CFF tab. These cells are blue and you do not need to edit them;
- - Any assumptions you make regarding your cash in-flows and cash out-flows should be both realistic and supportable. If you're starting a new business, we suggest being conservative with the cash flows you enter for the early months of trading;
- - It's important that your CFF corresponds with all of the objectives and activities you have outlined in your Business Plan. For example, if you have detailed plans for a three-month marketing campaign in your Business Plan then the costs for running this campaign should be clearly visible in your CFF;
- - Your CFF is based on a future estimate and while these figures will no doubt change over that trading period, it is a good amount of time for you - and us - to see how sustainable your plans are;
- - There is a commentary box at the bottom, for which you can use to explain any of costings, which you think will be of use to your Business Adviser	</t>
-    </r>
+    <t xml:space="preserve">This cashflow forecast uses the £2,500 REBEL Fund initial funding and the potential for a future £2000 funding from the UHI Business Competition.</t>
   </si>
   <si>
     <t>Key:</t>
@@ -1778,13 +1753,13 @@
     <t xml:space="preserve">Total anticipated sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Value of your Start Up Loan</t>
+    <t xml:space="preserve">REBEL Fund initial funding</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">Other sources of cash or equity</t>
+    <t xml:space="preserve">UHI Business Competition funding</t>
   </si>
   <si>
     <t xml:space="preserve">Existing assets for business purposes</t>
@@ -1811,7 +1786,10 @@
     <t xml:space="preserve">Business rates for your business premises</t>
   </si>
   <si>
-    <t xml:space="preserve">Utilities (gas, electricity, water)</t>
+    <t xml:space="preserve">Partnership incentives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiative partnerships</t>
   </si>
   <si>
     <t>Insurance</t>
@@ -1853,10 +1831,19 @@
     <t>Saplings</t>
   </si>
   <si>
+    <t xml:space="preserve">Tree saplings</t>
+  </si>
+  <si>
     <t xml:space="preserve">Event signage/materials</t>
   </si>
   <si>
+    <t xml:space="preserve">Event materials</t>
+  </si>
+  <si>
     <t xml:space="preserve">Promotion &amp; awareness materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promote to testers</t>
   </si>
   <si>
     <t xml:space="preserve">Launch or engagement events</t>
@@ -1865,7 +1852,13 @@
     <t xml:space="preserve">User incentives</t>
   </si>
   <si>
+    <t xml:space="preserve">Cash prizes to testers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Application publishing &amp; Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publishing costs</t>
   </si>
   <si>
     <t xml:space="preserve">Total cash out-flows (B)</t>
@@ -1904,7 +1897,7 @@
     <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1941,7 +1934,7 @@
     <font>
       <sz val="14.000000"/>
       <color theme="4"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1998,6 +1991,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.000000"/>
       <color theme="0"/>
@@ -2006,17 +2004,35 @@
     <font>
       <b/>
       <sz val="10.000000"/>
-      <color theme="4"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="0" tint="0"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="11.000000"/>
       <color theme="4"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -2034,6 +2050,12 @@
       <b/>
       <sz val="14.000000"/>
       <color theme="0"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="4"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -2751,7 +2773,7 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="142">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2927,38 +2949,38 @@
     <xf fontId="16" fillId="6" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="12" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="34" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="34" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="35" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="35" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="5" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="5" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="36" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="36" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2966,14 +2988,14 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="39" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="39" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="40" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="40" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2981,142 +3003,164 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="43" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="43" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="25" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="25" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="17" fillId="6" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="18" fillId="6" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="17" fillId="6" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="18" fillId="6" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="45" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="45" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="43" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="43" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="46" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="46" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="47" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="47" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="48" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="48" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="9" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="9" fillId="3" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="11" fillId="3" borderId="0" numFmtId="166" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="9" fillId="3" borderId="3" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="20" fillId="3" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="21" fillId="3" borderId="0" numFmtId="166" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="20" fillId="3" borderId="3" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="9" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="9" fillId="3" borderId="15" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="11" fillId="3" borderId="14" numFmtId="166" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="12" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="20" fillId="3" borderId="15" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="22" fillId="6" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="22" fillId="6" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="22" fillId="6" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="21" fillId="3" borderId="14" numFmtId="166" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="23" fillId="6" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="23" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="23" fillId="6" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="17" fillId="7" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="19" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="24" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="4" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="4" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="5" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="20" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf fontId="17" fillId="5" borderId="33" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="7" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="19" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="20" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="39" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="39" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="17" fillId="8" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="18" fillId="8" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="17" fillId="8" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="18" fillId="8" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="47" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="47" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="45" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="45" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="43" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="43" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="25" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="25" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="8" fillId="3" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="20" fillId="3" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="3" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="20" fillId="3" borderId="23" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="3" borderId="23" numFmtId="165" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="21" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="25" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="16" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="4" borderId="51" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="4" borderId="51" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="8" fillId="3" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf fontId="10" fillId="3" borderId="23" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="3" borderId="23" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="8" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="16" fillId="6" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="18" fillId="3" borderId="51" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="19" fillId="3" borderId="51" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="21" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="25" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="21" fillId="3" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="3" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="22" fillId="3" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="22" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="26" fillId="3" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="26" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="8" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="23" fillId="6" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="6" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="23" fillId="6" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="6" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="23" fillId="6" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="6" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="18" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="12" fillId="3" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3152,77 +3196,77 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="tc={008C007E-0023-4F06-A3B3-004C00380013}" id="{5ADDB92E-32B2-81F5-B0B9-6CC67C02872D}"/>
-  <person displayName="tc={000A0034-008D-4F81-B648-007800350074}" id="{D4431078-688D-C7FD-D275-3202B0C49A6B}"/>
-  <person displayName="tc={00410082-006F-446F-AB02-00A900AB0075}" id="{8DDBCFC0-3009-6FAA-25DC-0A62D7BD46E0}"/>
-  <person displayName="tc={00AF0088-00C3-44F0-9579-00E800BB008E}" id="{5C135379-EE25-534F-E829-F2EC2DFD66AE}"/>
-  <person displayName="tc={002900DC-007D-4F15-904A-00E600880094}" id="{8DD8BDCC-C856-D199-10EC-646E8FACB2F0}"/>
-  <person displayName="tc={00540021-003C-492A-B2FD-005F00F90049}" id="{D26F1070-EE3C-E553-B89A-A57B512CEFD6}"/>
-  <person displayName="tc={00D000E8-00D5-4F68-97B4-007A00E1000F}" id="{D9DDE86D-F04E-69D6-BB7E-E2CA6679019A}"/>
-  <person displayName="tc={00A100FD-00DA-43A9-9597-005C00B10024}" id="{67DEC394-6A1B-C35C-E683-CBEB3F78BB56}"/>
-  <person displayName="tc={00430049-00F8-4F7E-8CBF-008D00D300FA}" id="{A1369499-D873-054B-5741-C87840916A2B}"/>
-  <person displayName="tc={003D00C9-005D-4302-98A2-001100700003}" id="{9F229142-21B2-0DD2-DB8C-3EE915C1F6CF}"/>
-  <person displayName="tc={001400D8-0082-4168-89A2-00DC004C0084}" id="{DCFDB8C0-9116-0694-8509-83EA0FA27AF9}"/>
-  <person displayName="tc={0059000A-00A0-4A23-A0BD-00C300BE0010}" id="{2AE53E4D-DA7B-C1C5-6A3D-3AF2C798BCC4}"/>
-  <person displayName="tc={008E0068-0086-408D-AF6C-008A00FB0035}" id="{B503C0E1-A323-9BA7-9387-E5727E5298B7}"/>
-  <person displayName="tc={00A40077-0088-470B-9B0A-003D00D5002C}" id="{36D6CEA9-C02A-9B52-630E-923BD3F4F011}"/>
-  <person displayName="tc={00900010-00DE-49B2-85BB-00FC00C300A3}" id="{EFF75294-DC59-48EA-87AD-A96688202FF3}"/>
-  <person displayName="tc={00CA00DF-0022-42D1-ACE6-0078005D003D}" id="{7D246A04-F9BB-BA75-A6C4-6ED561E37B63}"/>
-  <person displayName="tc={001D00CE-0016-4306-B87C-00FF00550024}" id="{CDAC266F-F44A-209C-B211-18EFB3732F63}"/>
-  <person displayName="tc={00F4007C-0098-4D8E-8DCC-000200750039}" id="{A10F32A3-354D-04E6-9C03-B9843753C442}"/>
-  <person displayName="tc={00D5004E-003A-4E51-AAD5-00D900650090}" id="{9CB4320C-C04E-7357-7322-C9A785D23591}"/>
-  <person displayName="tc={005A0090-00B9-433D-B11B-00D600DF006A}" id="{B71E1A47-7DC7-E68A-A69D-7840023D80AA}"/>
-  <person displayName="tc={001F00E3-00B3-40F1-BFEC-00620040007D}" id="{5A3397C9-5BD7-A124-AF4B-ED4A3C4B46E3}"/>
-  <person displayName="tc={004400BD-002C-4741-B2D4-0078000A0074}" id="{24A08BC2-1A2C-773B-8782-708227408A32}"/>
-  <person displayName="tc={00EF00E6-000B-45B5-B026-00260062006D}" id="{A9AF69EF-99F5-4C2D-ADF3-144C08CEB9F9}"/>
-  <person displayName="tc={00C800FB-009E-400A-8779-000F0092007A}" id="{A0DA9740-EE28-073B-8AD1-CEC98CC8C67B}"/>
-  <person displayName="tc={007B00EF-0012-42B0-A029-00EC00880021}" id="{242CB47D-4461-6AAF-6882-F94EE70C0695}"/>
-  <person displayName="tc={003A0085-00FC-474A-B7D2-0006005600DC}" id="{6234FFDB-413D-20B9-2AAF-C0E2E4FC108D}"/>
-  <person displayName="tc={003900D8-00D3-4931-B0DA-00BD00B0009A}" id="{EB5AE7A3-583E-CBCD-D2D9-2AD488F11A34}"/>
-  <person displayName="tc={00DC00BA-009D-45CB-8F5C-00E200170018}" id="{C52988BF-0B7C-00D8-7F03-E8B5462341F4}"/>
-  <person displayName="tc={007E009F-0072-4832-93F2-00F30042007A}" id="{939DEE0E-7F8C-F61C-4CF7-F15E620B713A}"/>
-  <person displayName="tc={003000D4-0074-49F1-B0E3-00040071003C}" id="{72DFA2E8-0878-8E5E-6D2B-7A90C369AAE8}"/>
-  <person displayName="tc={005A00ED-00FB-404E-8518-00E60039001E}" id="{DBA11442-10FF-EE8A-D555-C6C849030DA8}"/>
-  <person displayName="tc={008D00E5-00EC-4ABC-8233-000E009B0075}" id="{40A7C497-7DBE-C071-3EA9-B1E62E8707AD}"/>
-  <person displayName="tc={00C300A0-0006-4B87-9CD2-000D0098004C}" id="{BC45C51C-51A3-CC46-FF90-EC44917520BA}"/>
-  <person displayName="tc={00D000B9-00AC-4796-AEFE-0019002800F9}" id="{584BA564-711D-2F30-5AA4-0D5A962F9EF6}"/>
-  <person displayName="tc={00A20063-004F-4A97-904E-002A00770042}" id="{2A8DC488-1D22-2EAC-F747-5F716C6D0AFA}"/>
-  <person displayName="tc={00AA00A1-00C1-456E-96A5-00CB00D700E2}" id="{A1F63897-8710-FFE0-5084-F3995215C611}"/>
-  <person displayName="tc={005B00CD-00BA-42B5-A4A0-009B003F0006}" id="{367795BA-8CF5-CD27-4B3E-1943E258DC6E}"/>
-  <person displayName="tc={003900E1-00A3-457B-8682-00FD006500B7}" id="{2E8A5410-902F-9314-5BBB-3B5544EBF69C}"/>
-  <person displayName="tc={00E8000B-00BA-4BCA-87AE-008F00D3006B}" id="{ADC288D6-5E41-C40B-DB59-847AFC7EF6A8}"/>
-  <person displayName="tc={00B700D2-00F4-487F-825A-008900B60054}" id="{1E0BF4D1-F8FC-6032-B259-8D8FA9493DEF}"/>
-  <person displayName="tc={00FB00ED-00E9-4692-8907-00E800E30001}" id="{03D32DA8-38F4-9CA8-ACE4-497DA1BDB297}"/>
-  <person displayName="tc={008C00EB-0093-4B2F-A57D-0041005400F3}" id="{E12E19DC-8C81-662A-FBDD-5E888BB16CB0}"/>
-  <person displayName="tc={004700AB-00D3-4A36-8747-003A00A60021}" id="{A7677CC0-055F-8232-962E-C7CC8F46142E}"/>
-  <person displayName="tc={00AE0015-0057-4B36-882A-00CD00C700D0}" id="{51A0C48A-A562-18EC-49B9-920A1EDA2769}"/>
-  <person displayName="tc={00A100F9-0096-4A73-A8ED-00A8002D00D7}" id="{6BE33B87-D988-CDAF-D490-5183367C86A8}"/>
-  <person displayName="tc={00B300CE-00DB-431F-86D6-0008005400A4}" id="{D072FE48-633D-D73A-9247-41D356CC9615}"/>
-  <person displayName="tc={006A003E-006E-43A3-8898-00DB00C00037}" id="{6AD293EC-64C6-D804-4F92-C39676BD8CC0}"/>
-  <person displayName="tc={00CE00C5-00FA-4A9A-9A2C-00A5001B0080}" id="{0B403B9B-994C-7461-4091-1DBD577A7595}"/>
-  <person displayName="tc={00EB0035-0010-4B54-9B49-00FC00B200E7}" id="{781A02A7-ECD1-735B-AD45-468D1F3726B4}"/>
-  <person displayName="tc={00530034-00A2-4256-9DF1-000D00F800C4}" id="{152C4C1B-57D5-391B-F772-FE12EF769CCC}"/>
-  <person displayName="tc={009900B9-0088-49D9-B4E4-0015000300E7}" id="{686AAE6A-2C12-D79C-B2FF-AC108B2CCEBF}"/>
-  <person displayName="tc={00D70092-00FF-4E47-9229-00E8000A0012}" id="{519602B8-6B48-E517-B296-88656AD96909}"/>
-  <person displayName="tc={002900E1-0025-42C1-B58D-006E00ED007A}" id="{2439759D-C14F-4274-FA99-56A8AC3FB558}"/>
-  <person displayName="tc={0030009A-007E-459C-AB1B-002100AD004A}" id="{152F39DF-8DBA-1640-0F51-42F98A9EB4D1}"/>
-  <person displayName="tc={00900007-0072-44DF-99A9-009100EF001F}" id="{3B1A6386-4FBA-EB8E-491B-5094992EB105}"/>
-  <person displayName="tc={00720044-00CC-42C7-A14B-00E0007E008D}" id="{7CF0F5BC-D365-A81E-08F6-931A60995547}"/>
-  <person displayName="tc={000200C3-003D-4A43-89DE-004600C60098}" id="{751E8703-8305-B06B-AB6F-3E7768550FF0}"/>
-  <person displayName="tc={00F200C9-00D7-4378-817E-008D005A003C}" id="{D048F121-4FA5-B0F5-2CF9-4E676FBCD0F7}"/>
-  <person displayName="tc={00F600F0-0092-483E-AB11-0096006E00E6}" id="{5C681748-F27F-2BA7-7E25-3586267A6BE1}"/>
-  <person displayName="tc={004600A3-00CB-48A0-BCBA-00D3005E00F9}" id="{25B379C8-AC8E-9298-7ACF-5C70A67B4D07}"/>
-  <person displayName="tc={001F00A5-00C0-4F61-AE66-00CB0025004A}" id="{A0FEF9E8-1A7C-9207-8C9D-1E8BCD64D4A1}"/>
-  <person displayName="tc={0042008A-0015-4672-B844-009A00E700A4}" id="{5B9B31FB-5AB2-90B4-96BB-A8A9F5BBE9DF}"/>
-  <person displayName="tc={0073003B-0052-4B7D-A143-006D00680045}" id="{CC42CBC4-0577-CC8A-A76C-305F2D82311C}"/>
-  <person displayName="tc={00FC0076-0062-445D-9D9E-000A0092005F}" id="{408B55F8-08F0-D2E3-FAC6-CAC5E9A78868}"/>
-  <person displayName="tc={0027004D-0016-43A3-BD4E-004600F20097}" id="{E09600ED-2D0B-A0BD-8264-60B6E1046853}"/>
-  <person displayName="tc={00C800A3-00A0-4D12-AA90-008D003B0089}" id="{0CCEB776-C9AC-1457-F7E2-88AC22FEFDB7}"/>
-  <person displayName="tc={00B100B2-0019-4A24-B868-005F00C30043}" id="{535B4AB3-55D5-EA5B-6CA7-B4A49E37E190}"/>
-  <person displayName="tc={003B0087-00FB-4E83-811E-00CD000100C6}" id="{35B918B5-8B50-BBFB-3700-CB2CAF8E5251}"/>
-  <person displayName="tc={00C30083-00A7-4C91-94BB-00FF00150088}" id="{08634309-F9D0-E6C0-EC54-67D782D98B42}"/>
-  <person displayName="tc={002B00DC-00E0-49E1-B78E-00B1004000F4}" id="{7D1091B0-330E-D353-668D-D7D950879D95}"/>
-  <person displayName="tc={0055001B-004E-43BB-B0A8-00B2006800E8}" id="{2EF0C0DA-CF16-341B-A4CF-77788E3921B2}"/>
+  <person displayName="tc={008C007E-0023-4F06-A3B3-004C00380013}" id="{A522B331-E646-4847-CF59-1DDE30AB93BA}"/>
+  <person displayName="tc={000A0034-008D-4F81-B648-007800350074}" id="{A6513472-E8FB-5D14-1551-95E530C17DE1}"/>
+  <person displayName="tc={00410082-006F-446F-AB02-00A900AB0075}" id="{94EDCE35-25A8-E48F-D91C-AA133D9DC902}"/>
+  <person displayName="tc={002900DC-007D-4F15-904A-00E600880094}" id="{BFFF5FD4-E3EA-F9BC-57AE-D789E820B9CC}"/>
+  <person displayName="tc={00AF0088-00C3-44F0-9579-00E800BB008E}" id="{728BF096-F289-561B-600F-3E3C291996B7}"/>
+  <person displayName="tc={00540021-003C-492A-B2FD-005F00F90049}" id="{BE748588-6AA6-757A-EDAA-0C4243EFA0A2}"/>
+  <person displayName="tc={0059000A-00A0-4A23-A0BD-00C300BE0010}" id="{E7808FB7-CFB2-044F-7A32-94569118C656}"/>
+  <person displayName="tc={008E0068-0086-408D-AF6C-008A00FB0035}" id="{D99FBB3B-0C93-1DA6-793D-3675318B1FBA}"/>
+  <person displayName="tc={00A40077-0088-470B-9B0A-003D00D5002C}" id="{D3D725FA-C0D3-21AB-4274-497365027F64}"/>
+  <person displayName="tc={00900010-00DE-49B2-85BB-00FC00C300A3}" id="{E6B89F48-B692-0758-D296-C25424323DC0}"/>
+  <person displayName="tc={00CA00DF-0022-42D1-ACE6-0078005D003D}" id="{4CECF2C1-5E13-2EBF-9916-221C8AE99381}"/>
+  <person displayName="tc={00D000E8-00D5-4F68-97B4-007A00E1000F}" id="{D6D7F2D3-2E0A-1B16-43AB-E5D68DEFC339}"/>
+  <person displayName="tc={00A100FD-00DA-43A9-9597-005C00B10024}" id="{A9B7908E-61B4-EC7A-5186-F66F44CC7645}"/>
+  <person displayName="tc={00430049-00F8-4F7E-8CBF-008D00D300FA}" id="{0BFB64EB-F629-B0AD-C10D-69A1FEB1FC31}"/>
+  <person displayName="tc={003D00C9-005D-4302-98A2-001100700003}" id="{1508E667-B0C1-93E1-C360-3B948892704C}"/>
+  <person displayName="tc={001400D8-0082-4168-89A2-00DC004C0084}" id="{3EF8E4E7-8066-FDE1-F53C-3B4E4CBC91E3}"/>
+  <person displayName="tc={001D00CE-0016-4306-B87C-00FF00550024}" id="{2F493785-3E56-A427-7C15-3891A37C96B1}"/>
+  <person displayName="tc={00F4007C-0098-4D8E-8DCC-000200750039}" id="{D768A2DB-59B4-88ED-EE8A-7F256EAE7289}"/>
+  <person displayName="tc={00D5004E-003A-4E51-AAD5-00D900650090}" id="{D2692A6A-6B6F-2CB5-3C1B-11C87FB9C33E}"/>
+  <person displayName="tc={005A0090-00B9-433D-B11B-00D600DF006A}" id="{9977A975-870C-D1B0-A255-300F7FD36322}"/>
+  <person displayName="tc={001F00E3-00B3-40F1-BFEC-00620040007D}" id="{C11C0333-9B77-E727-8816-A98C60ACD07A}"/>
+  <person displayName="tc={004400BD-002C-4741-B2D4-0078000A0074}" id="{ED4CCB77-BC49-D5F6-BFA6-487B44354D11}"/>
+  <person displayName="tc={00EF00E6-000B-45B5-B026-00260062006D}" id="{8DCAF8BA-6B71-0814-06CB-8F55EEBF82F9}"/>
+  <person displayName="tc={00C800FB-009E-400A-8779-000F0092007A}" id="{85B19261-0DCE-72FF-4222-DA00A8A2713A}"/>
+  <person displayName="tc={007B00EF-0012-42B0-A029-00EC00880021}" id="{17AAD085-023D-9378-BFAE-8D3B4855A741}"/>
+  <person displayName="tc={003A0085-00FC-474A-B7D2-0006005600DC}" id="{EE542798-4252-DFC0-C3B6-FEFBA4F6D6AC}"/>
+  <person displayName="tc={003900D8-00D3-4931-B0DA-00BD00B0009A}" id="{4BFC8BB7-AFF4-3E6E-7B46-9288FDDE2BA0}"/>
+  <person displayName="tc={00DC00BA-009D-45CB-8F5C-00E200170018}" id="{1B92D665-1617-7935-BE5B-82A961B1F514}"/>
+  <person displayName="tc={003000D4-0074-49F1-B0E3-00040071003C}" id="{69664200-F55F-ADF2-2B71-221885B90EF3}"/>
+  <person displayName="tc={007E009F-0072-4832-93F2-00F30042007A}" id="{81907BB7-5704-525B-6549-B07FD1751DB5}"/>
+  <person displayName="tc={005A00ED-00FB-404E-8518-00E60039001E}" id="{6BCC050F-9597-74EF-9E8F-27E07421AB4D}"/>
+  <person displayName="tc={00E8000B-00BA-4BCA-87AE-008F00D3006B}" id="{C9CCF6CA-72D3-618B-126C-D46DBD121E0A}"/>
+  <person displayName="tc={00B700D2-00F4-487F-825A-008900B60054}" id="{61866660-2F88-FD95-C538-46CB99E2AF0E}"/>
+  <person displayName="tc={00FB00ED-00E9-4692-8907-00E800E30001}" id="{8DF1D058-2E2E-AB7D-CC3D-2C55BE315492}"/>
+  <person displayName="tc={008C00EB-0093-4B2F-A57D-0041005400F3}" id="{085C3D00-E641-1AA3-D947-42ABD311A339}"/>
+  <person displayName="tc={004700AB-00D3-4A36-8747-003A00A60021}" id="{47B9859A-A478-9154-2713-4FA3C55B2CDE}"/>
+  <person displayName="tc={008D00E5-00EC-4ABC-8233-000E009B0075}" id="{24F30CDE-5B1B-70D2-E92D-63B6FFBA5226}"/>
+  <person displayName="tc={00C300A0-0006-4B87-9CD2-000D0098004C}" id="{E0840F77-7F4A-449A-4D89-F8CF75D54836}"/>
+  <person displayName="tc={00D000B9-00AC-4796-AEFE-0019002800F9}" id="{DD52069C-0AE0-A382-6E19-FF2F783F7851}"/>
+  <person displayName="tc={00A20063-004F-4A97-904E-002A00770042}" id="{8EA273C2-4B3F-7CCA-87A5-0A7047ABDDA9}"/>
+  <person displayName="tc={00AA00A1-00C1-456E-96A5-00CB00D700E2}" id="{87AB0278-5CF1-2706-53EA-A3ECB0B94E7A}"/>
+  <person displayName="tc={005B00CD-00BA-42B5-A4A0-009B003F0006}" id="{9C3D63EC-384D-E9F5-7DA8-0037C9CE57A7}"/>
+  <person displayName="tc={003900E1-00A3-457B-8682-00FD006500B7}" id="{0836C986-6F9E-F8E2-CB6B-FB020892E2A9}"/>
+  <person displayName="tc={00AE0015-0057-4B36-882A-00CD00C700D0}" id="{E7D4D466-6811-E378-91CC-55F39CBCC799}"/>
+  <person displayName="tc={00A100F9-0096-4A73-A8ED-00A8002D00D7}" id="{DCD5DEDE-39F2-0F46-F743-5A1AB53042EF}"/>
+  <person displayName="tc={00B300CE-00DB-431F-86D6-0008005400A4}" id="{A2091593-1B66-D2EA-A06C-FF020FCA5501}"/>
+  <person displayName="tc={006A003E-006E-43A3-8898-00DB00C00037}" id="{FDC6D8A8-37B3-79CA-4933-65C937A8B857}"/>
+  <person displayName="tc={00CE00C5-00FA-4A9A-9A2C-00A5001B0080}" id="{20BF0117-F354-B6D5-19DE-4E7B54D9FF22}"/>
+  <person displayName="tc={00EB0035-0010-4B54-9B49-00FC00B200E7}" id="{B858ADE7-F20C-7C01-416B-16F74A592379}"/>
+  <person displayName="tc={00530034-00A2-4256-9DF1-000D00F800C4}" id="{AEC472BD-460C-7E0F-0C75-431F1CE0B81A}"/>
+  <person displayName="tc={009900B9-0088-49D9-B4E4-0015000300E7}" id="{2BF10840-664D-1B6E-D423-99A614D4E1C2}"/>
+  <person displayName="tc={00D70092-00FF-4E47-9229-00E8000A0012}" id="{E9A5A57F-2EB8-C4DD-6711-D4B422625E74}"/>
+  <person displayName="tc={002900E1-0025-42C1-B58D-006E00ED007A}" id="{7E8F96EB-4DCE-FCE0-F075-EFC656DE0614}"/>
+  <person displayName="tc={0030009A-007E-459C-AB1B-002100AD004A}" id="{C5889666-3C78-01CF-1A0D-D82F00C4044D}"/>
+  <person displayName="tc={00900007-0072-44DF-99A9-009100EF001F}" id="{D71E892B-BDD0-8F95-0141-4AFAB160C4BB}"/>
+  <person displayName="tc={00720044-00CC-42C7-A14B-00E0007E008D}" id="{928943E5-2BDB-B74A-9AED-E2273B6CE05B}"/>
+  <person displayName="tc={000200C3-003D-4A43-89DE-004600C60098}" id="{EEBD212A-E56C-7F02-B91D-888590385AFC}"/>
+  <person displayName="tc={00F200C9-00D7-4378-817E-008D005A003C}" id="{FC617AA4-F25C-4A03-FD5B-25BED0ECC10B}"/>
+  <person displayName="tc={00F600F0-0092-483E-AB11-0096006E00E6}" id="{AB7C2522-BD20-E257-1CB2-F9B85C6D217D}"/>
+  <person displayName="tc={004600A3-00CB-48A0-BCBA-00D3005E00F9}" id="{681DAEE8-830C-1E1C-5593-4EC9C2ADA81D}"/>
+  <person displayName="tc={001F00A5-00C0-4F61-AE66-00CB0025004A}" id="{9C8E0905-2B68-7261-10C7-AC590618B95D}"/>
+  <person displayName="tc={0042008A-0015-4672-B844-009A00E700A4}" id="{3B5DEA9E-4086-97F3-E503-8D43CADE274B}"/>
+  <person displayName="tc={0073003B-0052-4B7D-A143-006D00680045}" id="{FB8BFD88-C737-7335-5261-93071B10FF30}"/>
+  <person displayName="tc={00FC0076-0062-445D-9D9E-000A0092005F}" id="{76C9F963-2FA4-57E6-3FE2-C6ED9C8082E6}"/>
+  <person displayName="tc={0027004D-0016-43A3-BD4E-004600F20097}" id="{41594502-0262-64A2-B428-98730E029476}"/>
+  <person displayName="tc={00C800A3-00A0-4D12-AA90-008D003B0089}" id="{4B70E306-8BB3-1585-8956-CDEEFF4DD22E}"/>
+  <person displayName="tc={00B100B2-0019-4A24-B868-005F00C30043}" id="{A0655BE1-D709-1912-101E-BAAB902983B1}"/>
+  <person displayName="tc={003B0087-00FB-4E83-811E-00CD000100C6}" id="{8AC383B7-D686-B91E-E454-914BFB51DAAA}"/>
+  <person displayName="tc={00C30083-00A7-4C91-94BB-00FF00150088}" id="{8E01ED78-13BB-93EF-87C1-721532955CC4}"/>
+  <person displayName="tc={002B00DC-00E0-49E1-B78E-00B1004000F4}" id="{D9C2D346-C3CC-08FE-5425-A41F27AB5E11}"/>
+  <person displayName="tc={0055001B-004E-43BB-B0A8-00B2006800E8}" id="{EBB704E9-A489-816E-0E8B-133781C1E1A1}"/>
 </personList>
 </file>
 
@@ -3706,309 +3750,309 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A21" personId="{5addb92e-32b2-81f5-b0b9-6cc67c02872d}" id="{882d51af-3269-1bf7-4b31-3a1fe6104ee7}" done="0">
+  <threadedComment ref="A21" personId="{A522B331-E646-4847-CF59-1DDE30AB93BA}" id="{882D51AF-3269-1BF7-4B31-3A1FE6104EE7}" done="0">
     <text xml:space="preserve">Explanation:
 Your forecast will run for 12-months from the start month you choose. This may be the month you expect to start your business or, if you have already started trading, the month you would like to receive the loan, if successful.
 Click on the cell to reveal a drop down list.
 </text>
   </threadedComment>
-  <threadedComment ref="A23" personId="{d4431078-688d-c7fd-d275-3202b0c49a6b}" id="{f371b72e-01bb-4eff-94b7-498a70678990}" done="0">
+  <threadedComment ref="A23" personId="{A6513472-E8FB-5D14-1551-95E530C17DE1}" id="{F371B72E-01BB-4EFF-94B7-498A70678990}" done="0">
     <text xml:space="preserve">Explanation
 This is where you list any money that you have coming in to your business such as product or service sales, equity or other investments and your Start Up Loan.
 The number of items you include will depend on your business model, but a typical revenue section usually includes between three and six items. If any of the pre-listed items are not relevant to your business, simply mark '0' in in the value field; and equally, if there are any items missing from the list, you can add them in the free fields at the bottom of the table.
 </text>
   </threadedComment>
-  <threadedComment ref="B23" personId="{8ddbcfc0-3009-6faa-25dc-0a62d7bd46e0}" id="{f7502d59-83b0-d240-5c48-7c39ef60fd2b}" done="0">
+  <threadedComment ref="B23" personId="{94EDCE35-25A8-E48F-D91C-AA133D9DC902}" id="{F7502D59-83B0-D240-5C48-7C39EF60FD2B}" done="0">
     <text xml:space="preserve">Explanation:
 Add a brief description for any items to help your Business Adviser understand each cash in-flow.
 </text>
   </threadedComment>
-  <threadedComment ref="P23" personId="{8dd8bdcc-c856-d199-10ec-646e8facb2f0}" id="{1b68213d-f6f6-f657-fa35-a6d00303f1e9}" done="0">
+  <threadedComment ref="P23" personId="{BFFF5FD4-E3EA-F9BC-57AE-D789E820B9CC}" id="{1B68213D-F6F6-F657-FA35-A6D00303F1E9}" done="0">
     <text xml:space="preserve">Explanation:
 This column will give you the 12-month total for each of your cash in-flows.
 </text>
   </threadedComment>
-  <threadedComment ref="C23" personId="{5c135379-ee25-534f-e829-f2ec2dfd66ae}" id="{634663f2-d2b3-3a7d-3e3b-991cb0d723cc}" done="0">
+  <threadedComment ref="C23" personId="{728BF096-F289-561B-600F-3E3C291996B7}" id="{634663F2-D2B3-3A7D-3E3B-991CB0D723CC}" done="0">
     <text xml:space="preserve">Explanation:
 Enter any money that you have prior to starting your 12-month forecast in this column. Leave it blank if this does not apply to some/any of your items.
 </text>
   </threadedComment>
-  <threadedComment ref="A24" personId="{d26f1070-ee3c-e553-b89a-a57b512cefd6}" id="{301ab3af-bfe9-fbaa-859d-261c589fa9f2}" done="0">
+  <threadedComment ref="A24" personId="{BE748588-6AA6-757A-EDAA-0C4243EFA0A2}" id="{301AB3AF-BFE9-FBAA-859D-261C589FA9F2}" done="0">
     <text xml:space="preserve">Explanation:
 This is value of the sales you anticipate making in the next 12-months.
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="K24" personId="{2ae53e4d-da7b-c1c5-6a3d-3af2c798bcc4}" id="{4f2a1241-44bf-d498-0ea2-c11a8d4815f4}" done="0">
+  <threadedComment ref="K24" personId="{E7808FB7-CFB2-044F-7A32-94569118C656}" id="{4F2A1241-44BF-D498-0EA2-C11A8D4815F4}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="L24" personId="{b503c0e1-a323-9ba7-9387-e5727e5298b7}" id="{b9bd068f-f1c0-5629-2808-14d6a02e9dba}" done="0">
+  <threadedComment ref="L24" personId="{D99FBB3B-0C93-1DA6-793D-3675318B1FBA}" id="{B9BD068F-F1C0-5629-2808-14D6A02E9DBA}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="M24" personId="{36d6cea9-c02a-9b52-630e-923bd3f4f011}" id="{9f58acf7-774a-dbb2-4396-b55c51337c6a}" done="0">
+  <threadedComment ref="M24" personId="{D3D725FA-C0D3-21AB-4274-497365027F64}" id="{9F58ACF7-774A-DBB2-4396-B55C51337C6A}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="N24" personId="{eff75294-dc59-48ea-87ad-a96688202ff3}" id="{ff35b7df-1374-6ae7-2864-78e270dde45f}" done="0">
+  <threadedComment ref="N24" personId="{E6B89F48-B692-0758-D296-C25424323DC0}" id="{FF35B7DF-1374-6AE7-2864-78E270DDE45F}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="O24" personId="{7d246a04-f9bb-ba75-a6c4-6ed561e37b63}" id="{9239f211-c845-074f-71ae-15b52f4914af}" done="0">
+  <threadedComment ref="O24" personId="{4CECF2C1-5E13-2EBF-9916-221C8AE99381}" id="{9239F211-C845-074F-71AE-15B52F4914AF}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="D24" personId="{d9dde86d-f04e-69d6-bb7e-e2ca6679019a}" id="{3ae576e4-ca1e-55a3-ec97-b3162a9c0046}" done="0">
+  <threadedComment ref="D24" personId="{D6D7F2D3-2E0A-1B16-43AB-E5D68DEFC339}" id="{3AE576E4-CA1E-55A3-EC97-B3162A9C0046}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="G24" personId="{67dec394-6a1b-c35c-e683-cbeb3f78bb56}" id="{ca82f6b1-ebfe-bcc6-0ad2-abf9eed412a1}" done="0">
+  <threadedComment ref="G24" personId="{A9B7908E-61B4-EC7A-5186-F66F44CC7645}" id="{CA82F6B1-EBFE-BCC6-0AD2-ABF9EED412A1}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="H24" personId="{a1369499-d873-054b-5741-c87840916a2b}" id="{0d7b761e-67cd-d103-48b9-6ba9fa5b3974}" done="0">
+  <threadedComment ref="H24" personId="{0BFB64EB-F629-B0AD-C10D-69A1FEB1FC31}" id="{0D7B761E-67CD-D103-48B9-6BA9FA5B3974}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="I24" personId="{9f229142-21b2-0dd2-db8c-3ee915c1f6cf}" id="{fbb78e0e-b469-79dc-21c9-b1051b3ca13e}" done="0">
+  <threadedComment ref="I24" personId="{1508E667-B0C1-93E1-C360-3B948892704C}" id="{FBB78E0E-B469-79DC-21C9-B1051B3CA13E}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="J24" personId="{dcfdb8c0-9116-0694-8509-83ea0fa27af9}" id="{3182d2cf-055a-7452-681f-336e0cf3edd5}" done="0">
+  <threadedComment ref="J24" personId="{3EF8E4E7-8066-FDE1-F53C-3B4E4CBC91E3}" id="{3182D2CF-055A-7452-681F-336E0CF3EDD5}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="A26" personId="{cdac266f-f44a-209c-b211-18efb3732f63}" id="{e5990929-1305-2dbe-2b28-4c8ac32f72e7}" done="0">
+  <threadedComment ref="A26" personId="{2F493785-3E56-A427-7C15-3891A37C96B1}" id="{E5990929-1305-2DBE-2B28-4C8AC32F72E7}" done="0">
     <text xml:space="preserve">Explanation:
 This might be money that you have personally put into the business or money that your business partners, private investors or other individuals have contributed. This could also be money that you have been gifted or inherited.
 </text>
   </threadedComment>
-  <threadedComment ref="A27" personId="{a10f32a3-354d-04e6-9c03-b9843753c442}" id="{38cf6407-3771-fb48-8e62-9033830e9cdb}" done="0">
+  <threadedComment ref="A27" personId="{D768A2DB-59B4-88ED-EE8A-7F256EAE7289}" id="{38CF6407-3771-FB48-8E62-9033830E9CDB}" done="0">
     <text xml:space="preserve">Explanation:
 An asset is an item or resource with value that you own and control and which has the potential to help you generate cash flow, reduce expenses or improve your sales in the future. 
 For example, this could be a vehicle, equipment or raw stock that you have purchased to produce your goods and/or services. 
 Please note, in order to balance this source of revenue, it will also be automatically reflected in the cash out-flows section of your cash flow forecast down below. That's because any value coming into the business has to have come out of somewhere.
 </text>
   </threadedComment>
-  <threadedComment ref="A28" personId="{9cb4320c-c04e-7357-7322-c9a785d23591}" id="{5caf605a-ebb2-9c14-fb1e-835ef20c1bf4}" done="0">
+  <threadedComment ref="A28" personId="{D2692A6A-6B6F-2CB5-3C1B-11C87FB9C33E}" id="{5CAF605A-EBB2-9C14-FB1E-835EF20C1BF4}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A29" personId="{b71e1a47-7dc7-e68a-a69d-7840023d80aa}" id="{1559d2dc-baa2-d59f-9ff9-099eafa1bce2}" done="0">
+  <threadedComment ref="A29" personId="{9977A975-870C-D1B0-A255-300F7FD36322}" id="{1559D2DC-BAA2-D59F-9FF9-099EAFA1BCE2}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A30" personId="{5a3397c9-5bd7-a124-af4b-ed4a3c4b46e3}" id="{62661412-6e4d-5f67-cfcb-58834a1f4a39}" done="0">
+  <threadedComment ref="A30" personId="{C11C0333-9B77-E727-8816-A98C60ACD07A}" id="{62661412-6E4D-5F67-CFCB-58834A1F4A39}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A31" personId="{24a08bc2-1a2c-773b-8782-708227408a32}" id="{5afdfb06-e9b9-ab1c-97bd-9e698185e3d1}" done="0">
+  <threadedComment ref="A31" personId="{ED4CCB77-BC49-D5F6-BFA6-487B44354D11}" id="{5AFDFB06-E9B9-AB1C-97BD-9E698185E3D1}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A32" personId="{a9af69ef-99f5-4c2d-adf3-144c08ceb9f9}" id="{1a016af7-264a-8326-9d49-8d2a0adfbead}" done="0">
+  <threadedComment ref="A32" personId="{8DCAF8BA-6B71-0814-06CB-8F55EEBF82F9}" id="{1A016AF7-264A-8326-9D49-8D2A0ADFBEAD}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A33" personId="{a0da9740-ee28-073b-8ad1-cec98cc8c67b}" id="{446e22c4-2eda-d01d-32c0-5bf5e2063d70}" done="0">
+  <threadedComment ref="A33" personId="{85B19261-0DCE-72FF-4222-DA00A8A2713A}" id="{446E22C4-2EDA-D01D-32C0-5BF5E2063D70}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A34" personId="{242cb47d-4461-6aaf-6882-f94ee70c0695}" id="{ae850658-0f17-3c29-d172-e8afe9b4837e}" done="0">
+  <threadedComment ref="A34" personId="{17AAD085-023D-9378-BFAE-8D3B4855A741}" id="{AE850658-0F17-3C29-D172-E8AFE9B4837E}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other income or cash in-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A35" personId="{6234ffdb-413d-20b9-2aaf-c0e2e4fc108d}" id="{73265cac-29c5-69dd-3c45-0292a3a478ce}" done="0">
+  <threadedComment ref="A35" personId="{EE542798-4252-DFC0-C3B6-FEFBA4F6D6AC}" id="{73265CAC-29C5-69DD-3C45-0292A3A478CE}" done="0">
     <text xml:space="preserve">Explanation:
 Your total cash in-flow is made up of all your individual sources of revenue added together.
 </text>
   </threadedComment>
-  <threadedComment ref="A39" personId="{eb5ae7a3-583e-cbcd-d2d9-2ad488f11a34}" id="{ac3d8698-9b3d-e95e-ea6c-134758a61ed8}" done="0">
+  <threadedComment ref="A39" personId="{4BFC8BB7-AFF4-3E6E-7B46-9288FDDE2BA0}" id="{AC3D8698-9B3D-E95E-EA6C-134758A61ED8}" done="0">
     <text xml:space="preserve">Explanation:
 This is where you list any of the costs your business incurs, how frequently it incurs them and when these costs will take place. 
 The number of items you include will depend on your business model.
 If any of the pre-listed items are not relevant to your business, simply mark '0' in in the value field; and equally, if there are any items missing from the list, you can add them in the free fields at the bottom of the table.
 </text>
   </threadedComment>
-  <threadedComment ref="B39" personId="{c52988bf-0b7c-00d8-7f03-e8b5462341f4}" id="{1637cc03-32bd-a4be-7eea-98b3d3b9235f}" done="0">
+  <threadedComment ref="B39" personId="{1B92D665-1617-7935-BE5B-82A961B1F514}" id="{1637CC03-32BD-A4BE-7EEA-98B3D3B9235F}" done="0">
     <text xml:space="preserve">Explanation:
 Add a brief description for any items to help your Business Adviser understand each cash out-flow.
 </text>
   </threadedComment>
-  <threadedComment ref="P39" personId="{72dfa2e8-0878-8e5e-6d2b-7a90c369aae8}" id="{aaed5316-baa9-6a6d-4652-32c815638106}" done="0">
+  <threadedComment ref="P39" personId="{69664200-F55F-ADF2-2B71-221885B90EF3}" id="{AAED5316-BAA9-6A6D-4652-32C815638106}" done="0">
     <text xml:space="preserve">Explanation:
 This column will give you the 12-month total for each of your cash out-flows.
 </text>
   </threadedComment>
-  <threadedComment ref="C39" personId="{939dee0e-7f8c-f61c-4cf7-f15e620b713a}" id="{5855cac1-58d0-ab89-3415-d090ad9d2ba4}" done="0">
+  <threadedComment ref="C39" personId="{81907BB7-5704-525B-6549-B07FD1751DB5}" id="{5855CAC1-58D0-AB89-3415-D090AD9D2BA4}" done="0">
     <text xml:space="preserve">Explanation:
 Enter any expenses that you have prior to starting your 12-month forecast in this column. Leave it blank if this does not apply to some/any of your items.
 </text>
   </threadedComment>
-  <threadedComment ref="A40" personId="{dba11442-10ff-ee8a-d555-c6c849030da8}" id="{f01c77f3-bede-b77e-7b53-84a0a9f23036}" done="0">
+  <threadedComment ref="A40" personId="{6BCC050F-9597-74EF-9E8F-27E07421AB4D}" id="{F01C77F3-BEDE-B77E-7B53-84A0A9F23036}" done="0">
     <text xml:space="preserve">Explanation:
 This is costs you expect to incur in order to produce all of your anticipated sales for the next 12-months. 
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="K40" personId="{adc288d6-5e41-c40b-db59-847afc7ef6a8}" id="{2ed74b0b-3d71-2cc8-626d-b729ca96166b}" done="0">
+  <threadedComment ref="K40" personId="{C9CCF6CA-72D3-618B-126C-D46DBD121E0A}" id="{2ED74B0B-3D71-2CC8-626D-B729CA96166B}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="L40" personId="{1e0bf4d1-f8fc-6032-b259-8d8fa9493def}" id="{8417ebe6-7ea4-4304-6f96-e87b7b4e0b43}" done="0">
+  <threadedComment ref="L40" personId="{61866660-2F88-FD95-C538-46CB99E2AF0E}" id="{8417EBE6-7EA4-4304-6F96-E87B7B4E0B43}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="M40" personId="{03d32da8-38f4-9ca8-ace4-497da1bdb297}" id="{53ff781a-2a83-ceb6-a0a7-06f3fc9e3ffd}" done="0">
+  <threadedComment ref="M40" personId="{8DF1D058-2E2E-AB7D-CC3D-2C55BE315492}" id="{53FF781A-2A83-CEB6-A0A7-06F3FC9E3FFD}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="N40" personId="{e12e19dc-8c81-662a-fbdd-5e888bb16cb0}" id="{f5220219-14c2-7a7f-380e-14538249b9ab}" done="0">
+  <threadedComment ref="N40" personId="{085C3D00-E641-1AA3-D947-42ABD311A339}" id="{F5220219-14C2-7A7F-380E-14538249B9AB}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="O40" personId="{a7677cc0-055f-8232-962e-c7cc8f46142e}" id="{3aeab38a-d7b4-e210-e230-cfab656d48bc}" done="0">
+  <threadedComment ref="O40" personId="{47B9859A-A478-9154-2713-4FA3C55B2CDE}" id="{3AEAB38A-D7B4-E210-E230-CFAB656D48BC}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="D40" personId="{40a7c497-7dbe-c071-3ea9-b1e62e8707ad}" id="{5b2d23fe-34dc-be59-9656-f43d8adc2074}" done="0">
+  <threadedComment ref="D40" personId="{24F30CDE-5B1B-70D2-E92D-63B6FFBA5226}" id="{5B2D23FE-34DC-BE59-9656-F43D8ADC2074}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="E40" personId="{bc45c51c-51a3-cc46-ff90-ec44917520ba}" id="{6df50f23-655e-5df7-16ad-befdd0bc96e1}" done="0">
+  <threadedComment ref="E40" personId="{E0840F77-7F4A-449A-4D89-F8CF75D54836}" id="{6DF50F23-655E-5DF7-16AD-BEFDD0BC96E1}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="F40" personId="{584ba564-711d-2f30-5aa4-0d5a962f9ef6}" id="{ae2bba9e-dc11-722d-c83a-2b12b5c4f6a8}" done="0">
+  <threadedComment ref="F40" personId="{DD52069C-0AE0-A382-6E19-FF2F783F7851}" id="{AE2BBA9E-DC11-722D-C83A-2B12B5C4F6A8}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="G40" personId="{2a8dc488-1d22-2eac-f747-5f716c6d0afa}" id="{c51ffbb3-ee99-6a9b-f5f0-d0917c62837a}" done="0">
+  <threadedComment ref="G40" personId="{8EA273C2-4B3F-7CCA-87A5-0A7047ABDDA9}" id="{C51FFBB3-EE99-6A9B-F5F0-D0917C62837A}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="H40" personId="{a1f63897-8710-ffe0-5084-f3995215c611}" id="{e1dcf7b9-90b3-b661-1de8-3b67359c5c7d}" done="0">
+  <threadedComment ref="H40" personId="{87AB0278-5CF1-2706-53EA-A3ECB0B94E7A}" id="{E1DCF7B9-90B3-B661-1DE8-3B67359C5C7D}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="I40" personId="{367795ba-8cf5-cd27-4b3e-1943e258dc6e}" id="{df1bac1b-7e7f-abcb-a67c-0d1077507e9d}" done="0">
+  <threadedComment ref="I40" personId="{9C3D63EC-384D-E9F5-7DA8-0037C9CE57A7}" id="{DF1BAC1B-7E7F-ABCB-A67C-0D1077507E9D}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="J40" personId="{2e8a5410-902f-9314-5bbb-3b5544ebf69c}" id="{2e42492d-90b7-6953-d2d3-8319d4a91e88}" done="0">
+  <threadedComment ref="J40" personId="{0836C986-6F9E-F8E2-CB6B-FB020892E2A9}" id="{2E42492D-90B7-6953-D2D3-8319D4A91E88}" done="0">
     <text xml:space="preserve">Explanation:
 This row will auto-populate based on the figures you entered in the 'Sales Assumption' tab so there is no need to update these cells.
 </text>
   </threadedComment>
-  <threadedComment ref="A41" personId="{51a0c48a-a562-18ec-49b9-920a1eda2769}" id="{104227df-22ef-c507-2eb9-53fac1bc6b74}" done="0">
+  <threadedComment ref="A41" personId="{E7D4D466-6811-E378-91CC-55F39CBCC799}" id="{104227DF-22EF-C507-2EB9-53FAC1BC6B74}" done="0">
     <text xml:space="preserve">Explanation:
 Any assets or resources with value that you own and control and have the potential to help you generate cash flow, reduce expenses or improve your sales in the future need to be reflected in both your cash in-flows and cash-out flows. 
 The first cell in this row (highlighted in green) is automatically populated based on what you entered in the cash in-flows section above. 
 </text>
   </threadedComment>
-  <threadedComment ref="C41" personId="{6be33b87-d988-cdaf-d490-5183367c86a8}" id="{a6932d2a-b3dd-d894-6c88-b67b25f9cf9a}" done="0">
+  <threadedComment ref="C41" personId="{DCD5DEDE-39F2-0F46-F743-5A1AB53042EF}" id="{A6932D2A-B3DD-D894-6C88-B67B25F9CF9A}" done="0">
     <text xml:space="preserve">Explanation:
 This is automatically populated based on the total amount of existing assets you declared above in order to balance your books.
 </text>
   </threadedComment>
-  <threadedComment ref="A42" personId="{d072fe48-633d-d73a-9247-41d356cc9615}" id="{6809d84c-d9c6-40b0-67fb-05262d615d77}" done="0">
+  <threadedComment ref="A42" personId="{A2091593-1B66-D2EA-A06C-FF020FCA5501}" id="{6809D84C-D9C6-40B0-67FB-05262D615D77}" done="0">
     <text xml:space="preserve">Explanation:
 You may be leasing your own venue, paying a membership fee to a hotdesking work hub, or working in a retail space. What cost do you incur to do this each month?
 </text>
   </threadedComment>
-  <threadedComment ref="A43" personId="{6ad293ec-64c6-d804-4f92-c39676bd8cc0}" id="{3bb02673-9ce8-c793-0c70-61be9881bcdf}" done="0">
+  <threadedComment ref="A43" personId="{FDC6D8A8-37B3-79CA-4933-65C937A8B857}" id="{3BB02673-9CE8-C793-0C70-61BE9881BCDF}" done="0">
     <text xml:space="preserve">Explanation:
 If you have a business premises or work from a home office, then it is likely that you are or will in future have to pay business rates to your local council.
 Check with your Local Authority if you're not sure.
 </text>
   </threadedComment>
-  <threadedComment ref="A44" personId="{0b403b9b-994c-7461-4091-1dbd577a7595}" id="{abaebfe0-7556-6190-cf03-a4b8ea0839b7}" done="0">
+  <threadedComment ref="A44" personId="{20BF0117-F354-B6D5-19DE-4E7B54D9FF22}" id="{ABAEBFE0-7556-6190-CF03-A4B8EA0839B7}" done="0">
     <text xml:space="preserve">Explanation:
 You can group all of your utilities together into one monthly line item. 
 This might include things like your gas, electricity or water payments you make for your business. 
 If you work from your home office, you may be entitled to charge a portion of your utilities expenses against the business.
 </text>
   </threadedComment>
-  <threadedComment ref="A45" personId="{781a02a7-ecd1-735b-ad45-468d1f3726b4}" id="{a2bdd411-2cbf-30eb-a448-a0dd5b228658}" done="0">
+  <threadedComment ref="A45" personId="{B858ADE7-F20C-7C01-416B-16F74A592379}" id="{A2BDD411-2CBF-30EB-A448-A0DD5B228658}" done="0">
     <text xml:space="preserve">Explanation:
 If you haven't already, it is important to consider business insurance to cover you for any range of circumstances that may emerge that are out of your control.
 This could be anything from premises, stock or equipment insurance to personal or employee liability insurance.
 </text>
   </threadedComment>
-  <threadedComment ref="A46" personId="{152c4c1b-57d5-391b-f772-fe12ef769ccc}" id="{9c7d0011-60bd-79df-8a1a-91403ef77edc}" done="0">
+  <threadedComment ref="A46" personId="{AEC472BD-460C-7E0F-0C75-431F1CE0B81A}" id="{9C7D0011-60BD-79DF-8A1A-91403EF77EDC}" done="0">
     <text xml:space="preserve">Explanation:
 Telephone and internet access is likely to be essential for almost every business type. 
 Think about all the costs you currently incur or will incur in the next 12-months for this line item across your business, including the cost for each individual staff member if relevant.
 </text>
   </threadedComment>
-  <threadedComment ref="A47" personId="{686aae6a-2c12-d79c-b2ff-ac108b2ccebf}" id="{5210a8ae-646e-e94a-4779-985a3280ac02}" done="0">
+  <threadedComment ref="A47" personId="{2BF10840-664D-1B6E-D423-99A614D4E1C2}" id="{5210A8AE-646E-E94A-4779-985A3280AC02}" done="0">
     <text xml:space="preserve">Explanation:
 Think about what you have detailed in your business plan. What are the regular marketing and advertising costs that you incur to promote your business and drive sales? 
 </text>
   </threadedComment>
-  <threadedComment ref="A48" personId="{519602b8-6b48-e517-b296-88656ad96909}" id="{b4026a48-5250-6578-aa06-07446ec6894c}" done="0">
+  <threadedComment ref="A48" personId="{E9A5A57F-2EB8-C4DD-6711-D4B422625E74}" id="{B4026A48-5250-6578-AA06-07446EC6894C}" done="0">
     <text xml:space="preserve">Explanation:
 If you use a vehicle to operate your business, how much do you spend each month on fuel, insurance, registration, repairs?
 </text>
   </threadedComment>
-  <threadedComment ref="A49" personId="{2439759d-c14f-4274-fa99-56a8ac3fb558}" id="{35fc713c-c9c5-c0a5-a9a4-9b7a6d70bfc5}" done="0">
+  <threadedComment ref="A49" personId="{7E8F96EB-4DCE-FCE0-F075-EFC656DE0614}" id="{35FC713C-C9C5-C0A5-A9A4-9B7A6D70BFC5}" done="0">
     <text xml:space="preserve">Explanation:
 This is the cost of purchasing or leasing equipment to produce your product(s) and/or service(s), or the use of software to support you in delivering your product(s) and/or service(s).
 </text>
   </threadedComment>
-  <threadedComment ref="A50" personId="{152f39df-8dba-1640-0f51-42f98a9eb4d1}" id="{72b4233f-9e08-bb03-b475-099470f1e367}" done="0">
+  <threadedComment ref="A50" personId="{C5889666-3C78-01CF-1A0D-D82F00C4044D}" id="{72B4233F-9E08-BB03-B475-099470F1E367}" done="0">
     <text xml:space="preserve">Explanation:
 Every business incurs administrative costs, whether it is postage stamps to send out your product(s) and/or service(s), stationery products for you and your team, or printing facilities.
 </text>
   </threadedComment>
-  <threadedComment ref="A51" personId="{3b1a6386-4fba-eb8e-491b-5094992eb105}" id="{0e8e5db2-bb19-7969-3f4f-949488887d52}" done="0">
+  <threadedComment ref="A51" personId="{D71E892B-BDD0-8F95-0141-4AFAB160C4BB}" id="{0E8E5DB2-BB19-7969-3F4F-949488887D52}" done="0">
     <text xml:space="preserve">Explanation:
 If you run a product based business then you may incur monthly fees for transport and delivery of your goods.
 </text>
   </threadedComment>
-  <threadedComment ref="A52" personId="{7cf0f5bc-d365-a81e-08f6-931a60995547}" id="{bcd66f2e-18c5-8f5e-e055-aa7f412fb090}" done="0">
+  <threadedComment ref="A52" personId="{928943E5-2BDB-B74A-9AED-E2273B6CE05B}" id="{BCD66F2E-18C5-8F5E-E055-AA7F412FB090}" done="0">
     <text xml:space="preserve">Explanation:
 Think about any professional services you need to use in order to manage your business. This might be on a retainer or ad-hoc basis.
 For example, a lawyer, accountant, designer or marketing consultant.
 </text>
   </threadedComment>
-  <threadedComment ref="A53" personId="{751e8703-8305-b06b-ab6f-3e7768550ff0}" id="{7f51f8d1-c8f0-a84d-f9a8-74a8b5aa15c3}" done="0">
+  <threadedComment ref="A53" personId="{EEBD212A-E56C-7F02-B91D-888590385AFC}" id="{7F51F8D1-C8F0-A84D-F9A8-74A8B5AA15C3}" done="0">
     <text xml:space="preserve">Explanation:
 These cells are designed to auto-populate based on the responses in your Personal Survival Budget (PSB). It will only display figures if your PSB is in deficit, as this means you will require you will need to take more from the business each month in order to meet your personal expenses. 
 If your PSB  is in surplus, then these cells will stay blank as this means you are already meeting your personal expenses every month without drawing additional money from your business.
@@ -4016,7 +4060,7 @@
 If you haven't completed your PSB yet, then this will remain blank until you do.
 </text>
   </threadedComment>
-  <threadedComment ref="D53" personId="{d048f121-4fa5-b0f5-2cf9-4e676fbcd0f7}" id="{79bf3859-14e7-106a-bacb-6b94fe278f8b}" done="0">
+  <threadedComment ref="D53" personId="{FC617AA4-F25C-4A03-FD5B-25BED0ECC10B}" id="{79BF3859-14E7-106A-BACB-6B94FE278F8B}" done="0">
     <text xml:space="preserve">Explanation:
 These cells are designed to auto-populate based on the responses in your Personal Survival Budget (PSB). It will only display figures if your PSB is in deficit, as this means you will require you will need to take more from the business each month in order to meet your personal expenses. 
 If your PSB  is in surplus, then these cells will stay blank as this means you are already meeting your personal expenses every month without drawing additional money from your business.
@@ -4024,74 +4068,74 @@
 If you haven't completed your Personal Survival Budget yet, then this will remain blank until you do.
 </text>
   </threadedComment>
-  <threadedComment ref="A54" personId="{5c681748-f27f-2ba7-7e25-3586267a6be1}" id="{b5f35f55-2424-b548-b367-622dcf753a3e}" done="0">
+  <threadedComment ref="A54" personId="{AB7C2522-BD20-E257-1CB2-F9B85C6D217D}" id="{B5F35F55-2424-B548-B367-622DCF753A3E}" done="0">
     <text xml:space="preserve">Explanation:
 This is for any additional money you would like to take from the business as your salary, above and beyond your Personal Survival Budget (PSB) needs. 
 For example, if your PSB is currently in surplus (you already have enough money to meet your personal expenses) but you would like to take a further £200 for yourself from the business each month, then this should be added in here.
 </text>
   </threadedComment>
-  <threadedComment ref="A55" personId="{25b379c8-ac8e-9298-7acf-5c70a67b4d07}" id="{9d66f356-3ca5-c191-8a99-35a53de775ec}" done="0">
+  <threadedComment ref="A55" personId="{681DAEE8-830C-1E1C-5593-4EC9C2ADA81D}" id="{9D66F356-3CA5-C191-8A99-35A53DE775EC}" done="0">
     <text xml:space="preserve">Explanation:
 If you hire staff, whether full time or part time, then this is where you can reflect the amount of money you spend each month on staff salaries, national insurance contributions and staff pensions etc.
 </text>
   </threadedComment>
-  <threadedComment ref="A56" personId="{a0fef9e8-1a7c-9207-8c9d-1e8bcd64d4a1}" id="{baa9df04-efd9-7be4-c5c9-2b1a18f98aae}" done="0">
+  <threadedComment ref="A56" personId="{9C8E0905-2B68-7261-10C7-AC590618B95D}" id="{BAA9DF04-EFD9-7BE4-C5C9-2B1A18F98AAE}" done="0">
     <text xml:space="preserve">Explanation:
 This should be the monthly amount you pay for your Start Up Loan.
 </text>
   </threadedComment>
-  <threadedComment ref="A58" personId="{5b9b31fb-5ab2-90b4-96bb-a8a9f5bbe9df}" id="{f6502e8f-2091-03e3-6e3b-d3ee4ee2b584}" done="0">
+  <threadedComment ref="A58" personId="{3B5DEA9E-4086-97F3-E503-8D43CADE274B}" id="{F6502E8F-2091-03E3-6E3B-D3EE4EE2B584}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other expenses or cash out-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A59" personId="{cc42cbc4-0577-cc8a-a76c-305f2d82311c}" id="{20ea3103-cf0f-3469-a596-ee8da6370d8c}" done="0">
+  <threadedComment ref="A59" personId="{FB8BFD88-C737-7335-5261-93071B10FF30}" id="{20EA3103-CF0F-3469-A596-EE8DA6370D8C}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other expenses or cash out-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A60" personId="{408b55f8-08f0-d2e3-fac6-cac5e9a78868}" id="{d895b3cd-2bcd-1ed4-1036-eaaca1b3783d}" done="0">
+  <threadedComment ref="A60" personId="{76C9F963-2FA4-57E6-3FE2-C6ED9C8082E6}" id="{D895B3CD-2BCD-1ED4-1036-EAACA1B3783D}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other expenses or cash out-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A61" personId="{e09600ed-2d0b-a0bd-8264-60b6e1046853}" id="{6324958d-5d3f-fae7-c89f-3fc4bbc1ffda}" done="0">
+  <threadedComment ref="A61" personId="{41594502-0262-64A2-B428-98730E029476}" id="{6324958D-5D3F-FAE7-C89F-3FC4BBC1FFDA}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other expenses or cash out-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A62" personId="{0cceb776-c9ac-1457-f7e2-88ac22fefdb7}" id="{c52f62ad-2dd7-aec6-0e55-80e9af53b1f9}" done="0">
+  <threadedComment ref="A62" personId="{4B70E306-8BB3-1585-8956-CDEEFF4DD22E}" id="{C52F62AD-2DD7-AEC6-0E55-80E9AF53B1F9}" done="0">
     <text xml:space="preserve">Explanation:
 Use these fields if your business has any other expenses or cash out-flows that are not covered in the above. 
 Provide a description of these items in the next field.
 </text>
   </threadedComment>
-  <threadedComment ref="A63" personId="{535b4ab3-55d5-ea5b-6ca7-b4a49e37e190}" id="{d428a997-f208-389a-09cd-7381a0844d47}" done="0">
+  <threadedComment ref="A63" personId="{A0655BE1-D709-1912-101E-BAAB902983B1}" id="{D428A997-F208-389A-09CD-7381A0844D47}" done="0">
     <text xml:space="preserve">Explanation:
 Your total cash out-flow is made up of all your expenses added together.
 </text>
   </threadedComment>
-  <threadedComment ref="B65" personId="{35b918b5-8b50-bbfb-3700-cb2caf8e5251}" id="{770b60d9-d001-5d79-1b4d-a6f623dcd238}" done="0">
+  <threadedComment ref="B65" personId="{8AC383B7-D686-B91E-E454-914BFB51DAAA}" id="{770B60D9-D001-5D79-1B4D-A6F623DCD238}" done="0">
     <text xml:space="preserve">Explanation:
 Your net cash flow tells you the difference between what is coming in and what is going out of your business on a monthly basis.
 </text>
   </threadedComment>
-  <threadedComment ref="B67" personId="{08634309-f9d0-e6c0-ec54-67d782d98b42}" id="{05a2c7ac-cc92-dbe1-c98b-9e0ad6f89599}" done="0">
+  <threadedComment ref="B67" personId="{8E01ED78-13BB-93EF-87C1-721532955CC4}" id="{05A2C7AC-CC92-DBE1-C98B-9E0AD6F89599}" done="0">
     <text xml:space="preserve">Explanation:
 This is the amount of money that you have available for your business at the start of each month. You'll see this number will auto-update for each month, based on the previous months' cash flow. 
 </text>
   </threadedComment>
-  <threadedComment ref="B69" personId="{7d1091b0-330e-d353-668d-d7d950879d95}" id="{46c23f41-f179-4967-070f-530d995ea988}" done="0">
+  <threadedComment ref="B69" personId="{D9C2D346-C3CC-08FE-5425-A41F27AB5E11}" id="{46C23F41-F179-4967-070F-530D995EA988}" done="0">
     <text xml:space="preserve">Explanation:
 This is your anticipated financial position at the end of each month, once you have brought in all your revenue, paid all your expenses and balanced your books. 
 This figure is calculated by adding together whatever money is recorded in your net cash flow for a particular month with the opening balance at the start of that month.
 </text>
   </threadedComment>
-  <threadedComment ref="B76" personId="{2ef0c0da-cf16-341b-a4cf-77788e3921b2}" id="{f0e94bc5-6fe1-2ab8-14f8-d84e8a63ff88}" done="0">
+  <threadedComment ref="B76" personId="{EBB704E9-A489-816E-0E8B-133781C1E1A1}" id="{F0E94BC5-6FE1-2AB8-14F8-D84E8A63FF88}" done="0">
     <text xml:space="preserve">Explanation:
 This is a good place to write any notes that you want your Business Adviser to take into account when reviewing your Cash Flow Forecast.
 This might be if something needs further explanation or if you want to more clearly reference a figure back to something in your Business Plan.
@@ -4103,6 +4147,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="38.7109375"/>
+    <col customWidth="1" min="2" max="2" width="22.8515625"/>
+    <col customWidth="1" min="3" max="3" width="14.8515625"/>
+  </cols>
   <sheetData>
     <row r="1" ht="26.25">
       <c r="A1" s="1" t="s">
@@ -4142,7 +4191,7 @@
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" ht="18.75">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -4165,7 +4214,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" ht="18.75">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -4338,7 +4387,7 @@
       </c>
       <c r="P12" s="28"/>
     </row>
-    <row r="13" ht="24.75" customHeight="1">
+    <row r="13" ht="24.75" hidden="1" customHeight="1">
       <c r="A13" s="29"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -4358,7 +4407,7 @@
       </c>
       <c r="P13" s="34"/>
     </row>
-    <row r="14" ht="14.25">
+    <row r="14" ht="14.25" hidden="1">
       <c r="A14" s="35"/>
       <c r="B14" s="35"/>
       <c r="C14" s="36"/>
@@ -4421,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="45">
-        <v>5.9999999999999998e-002</v>
+        <v>0</v>
       </c>
       <c r="C17" s="42"/>
       <c r="D17" s="42"/>
@@ -4650,7 +4699,7 @@
         <v>#REF!</v>
       </c>
       <c r="P24" s="69" t="e">
-        <f>SUM(C24:O24)</f>
+        <f t="shared" ref="P24:P52" si="0">SUM(C24:O24)</f>
         <v>#REF!</v>
       </c>
     </row>
@@ -4678,9 +4727,7 @@
       <c r="H25" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="71" t="s">
-        <v>20</v>
-      </c>
+      <c r="I25" s="71"/>
       <c r="J25" s="71" t="s">
         <v>20</v>
       </c>
@@ -4700,7 +4747,7 @@
         <v>20</v>
       </c>
       <c r="P25" s="72">
-        <f>SUM(C25:O25)</f>
+        <f t="shared" si="0"/>
         <v>2500</v>
       </c>
     </row>
@@ -4710,7 +4757,7 @@
       </c>
       <c r="B26" s="66"/>
       <c r="C26" s="67">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D26" s="67">
         <v>0</v>
@@ -4749,8 +4796,8 @@
         <v>0</v>
       </c>
       <c r="P26" s="72">
-        <f>SUM(C26:O26)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" ht="14.25">
@@ -4798,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="72">
-        <f>SUM(C27:O27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4847,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="72">
-        <f>SUM(C28:O28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4896,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="72">
-        <f>SUM(C29:O29)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4945,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="72">
-        <f>SUM(C30:O30)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4994,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="77">
-        <f>SUM(C31:O31)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5043,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="81">
-        <f>SUM(C32:O32)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5092,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="81">
-        <f>SUM(C33:O33)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5141,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="81">
-        <f>SUM(C34:O34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -5152,7 +5199,7 @@
       <c r="B35" s="83"/>
       <c r="C35" s="84">
         <f>SUM(C24:C34)</f>
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="D35" s="85" t="e">
         <f>SUM(D24:D34)</f>
@@ -5203,7 +5250,7 @@
         <v>#REF!</v>
       </c>
       <c r="P35" s="88" t="e">
-        <f>SUM(C35:O35)</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
     </row>
@@ -5243,82 +5290,82 @@
       <c r="O37" s="92"/>
       <c r="P37" s="91"/>
     </row>
-    <row r="38" ht="15">
+    <row r="38" ht="15" hidden="1">
       <c r="A38" s="93"/>
       <c r="B38" s="93"/>
       <c r="C38" s="94"/>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="58"/>
-      <c r="O38" s="59"/>
-      <c r="P38" s="95"/>
-    </row>
-    <row r="39" ht="12" customHeight="1">
+      <c r="E38" s="96"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="96"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="96"/>
+      <c r="N38" s="96"/>
+      <c r="O38" s="97"/>
+      <c r="P38" s="98"/>
+    </row>
+    <row r="39" ht="26.25" customHeight="1">
       <c r="A39" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B39" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="63">
+      <c r="D39" s="100">
         <v>1</v>
       </c>
-      <c r="E39" s="63">
+      <c r="E39" s="100">
         <v>2</v>
       </c>
-      <c r="F39" s="63">
+      <c r="F39" s="100">
         <v>3</v>
       </c>
-      <c r="G39" s="63">
+      <c r="G39" s="100">
         <v>4</v>
       </c>
-      <c r="H39" s="63">
+      <c r="H39" s="100">
         <v>5</v>
       </c>
-      <c r="I39" s="63">
+      <c r="I39" s="100">
         <v>6</v>
       </c>
-      <c r="J39" s="63">
+      <c r="J39" s="100">
         <v>7</v>
       </c>
-      <c r="K39" s="63">
+      <c r="K39" s="100">
         <v>8</v>
       </c>
-      <c r="L39" s="63">
+      <c r="L39" s="100">
         <v>9</v>
       </c>
-      <c r="M39" s="63">
+      <c r="M39" s="100">
         <v>10</v>
       </c>
-      <c r="N39" s="63">
+      <c r="N39" s="100">
         <v>11</v>
       </c>
-      <c r="O39" s="63">
+      <c r="O39" s="100">
         <v>12</v>
       </c>
-      <c r="P39" s="64" t="s">
+      <c r="P39" s="101" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="96" t="s">
+      <c r="A40" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="97"/>
-      <c r="C40" s="98">
+      <c r="B40" s="103"/>
+      <c r="C40" s="104">
         <v>0</v>
       </c>
       <c r="D40" s="68" t="e">
@@ -5370,654 +5417,656 @@
         <v>#REF!</v>
       </c>
       <c r="P40" s="69" t="e">
-        <f>SUM(C40:O40)</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="A41" s="96" t="s">
+      <c r="A41" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="97">
-        <v>0</v>
-      </c>
-      <c r="C41" s="99">
+      <c r="B41" s="103">
+        <v>0</v>
+      </c>
+      <c r="C41" s="105">
         <f>SUM(C27)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="98">
-        <v>0</v>
-      </c>
-      <c r="E41" s="98">
-        <v>0</v>
-      </c>
-      <c r="F41" s="98">
-        <v>0</v>
-      </c>
-      <c r="G41" s="98">
-        <v>0</v>
-      </c>
-      <c r="H41" s="98">
-        <v>0</v>
-      </c>
-      <c r="I41" s="98">
-        <v>0</v>
-      </c>
-      <c r="J41" s="98">
-        <v>0</v>
-      </c>
-      <c r="K41" s="98">
-        <v>0</v>
-      </c>
-      <c r="L41" s="98">
-        <v>0</v>
-      </c>
-      <c r="M41" s="98">
-        <v>0</v>
-      </c>
-      <c r="N41" s="98">
-        <v>0</v>
-      </c>
-      <c r="O41" s="98">
+      <c r="D41" s="104">
+        <v>0</v>
+      </c>
+      <c r="E41" s="104">
+        <v>0</v>
+      </c>
+      <c r="F41" s="104">
+        <v>0</v>
+      </c>
+      <c r="G41" s="104">
+        <v>0</v>
+      </c>
+      <c r="H41" s="104">
+        <v>0</v>
+      </c>
+      <c r="I41" s="104">
+        <v>0</v>
+      </c>
+      <c r="J41" s="104">
+        <v>0</v>
+      </c>
+      <c r="K41" s="104">
+        <v>0</v>
+      </c>
+      <c r="L41" s="104">
+        <v>0</v>
+      </c>
+      <c r="M41" s="104">
+        <v>0</v>
+      </c>
+      <c r="N41" s="104">
+        <v>0</v>
+      </c>
+      <c r="O41" s="104">
         <v>0</v>
       </c>
       <c r="P41" s="72">
-        <f>SUM(C41:O41)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="A42" s="96" t="s">
+      <c r="A42" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="97"/>
-      <c r="C42" s="98">
-        <v>0</v>
-      </c>
-      <c r="D42" s="98">
-        <v>0</v>
-      </c>
-      <c r="E42" s="98">
-        <v>0</v>
-      </c>
-      <c r="F42" s="98">
-        <v>0</v>
-      </c>
-      <c r="G42" s="98">
-        <v>0</v>
-      </c>
-      <c r="H42" s="98">
-        <v>0</v>
-      </c>
-      <c r="I42" s="98">
-        <v>0</v>
-      </c>
-      <c r="J42" s="98">
-        <v>0</v>
-      </c>
-      <c r="K42" s="98">
-        <v>0</v>
-      </c>
-      <c r="L42" s="98">
-        <v>0</v>
-      </c>
-      <c r="M42" s="98">
-        <v>0</v>
-      </c>
-      <c r="N42" s="98">
-        <v>0</v>
-      </c>
-      <c r="O42" s="98">
+      <c r="B42" s="103"/>
+      <c r="C42" s="104">
+        <v>0</v>
+      </c>
+      <c r="D42" s="104">
+        <v>0</v>
+      </c>
+      <c r="E42" s="104">
+        <v>0</v>
+      </c>
+      <c r="F42" s="104">
+        <v>0</v>
+      </c>
+      <c r="G42" s="104">
+        <v>0</v>
+      </c>
+      <c r="H42" s="104">
+        <v>0</v>
+      </c>
+      <c r="I42" s="104">
+        <v>0</v>
+      </c>
+      <c r="J42" s="104">
+        <v>0</v>
+      </c>
+      <c r="K42" s="104">
+        <v>0</v>
+      </c>
+      <c r="L42" s="104">
+        <v>0</v>
+      </c>
+      <c r="M42" s="104">
+        <v>0</v>
+      </c>
+      <c r="N42" s="104">
+        <v>0</v>
+      </c>
+      <c r="O42" s="104">
         <v>0</v>
       </c>
       <c r="P42" s="72">
-        <f>SUM(C42:O42)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="A43" s="96" t="s">
+      <c r="A43" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="97"/>
-      <c r="C43" s="98">
-        <v>0</v>
-      </c>
-      <c r="D43" s="98">
-        <v>0</v>
-      </c>
-      <c r="E43" s="98">
-        <v>0</v>
-      </c>
-      <c r="F43" s="98">
-        <v>0</v>
-      </c>
-      <c r="G43" s="98">
-        <v>0</v>
-      </c>
-      <c r="H43" s="98">
-        <v>0</v>
-      </c>
-      <c r="I43" s="98">
-        <v>0</v>
-      </c>
-      <c r="J43" s="98">
-        <v>0</v>
-      </c>
-      <c r="K43" s="98">
-        <v>0</v>
-      </c>
-      <c r="L43" s="98">
-        <v>0</v>
-      </c>
-      <c r="M43" s="98">
-        <v>0</v>
-      </c>
-      <c r="N43" s="98">
-        <v>0</v>
-      </c>
-      <c r="O43" s="98">
+      <c r="B43" s="103"/>
+      <c r="C43" s="104">
+        <v>0</v>
+      </c>
+      <c r="D43" s="104">
+        <v>0</v>
+      </c>
+      <c r="E43" s="104">
+        <v>0</v>
+      </c>
+      <c r="F43" s="104">
+        <v>0</v>
+      </c>
+      <c r="G43" s="104">
+        <v>0</v>
+      </c>
+      <c r="H43" s="104">
+        <v>0</v>
+      </c>
+      <c r="I43" s="104">
+        <v>0</v>
+      </c>
+      <c r="J43" s="104">
+        <v>0</v>
+      </c>
+      <c r="K43" s="104">
+        <v>0</v>
+      </c>
+      <c r="L43" s="104">
+        <v>0</v>
+      </c>
+      <c r="M43" s="104">
+        <v>0</v>
+      </c>
+      <c r="N43" s="104">
+        <v>0</v>
+      </c>
+      <c r="O43" s="104">
         <v>0</v>
       </c>
       <c r="P43" s="72">
-        <f>SUM(C43:O43)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="A44" s="96" t="s">
+      <c r="A44" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="97"/>
-      <c r="C44" s="98">
-        <v>0</v>
-      </c>
-      <c r="D44" s="98">
-        <v>0</v>
-      </c>
-      <c r="E44" s="98">
-        <v>0</v>
-      </c>
-      <c r="F44" s="98">
-        <v>0</v>
-      </c>
-      <c r="G44" s="98">
-        <v>0</v>
-      </c>
-      <c r="H44" s="98">
-        <v>0</v>
-      </c>
-      <c r="I44" s="98">
-        <v>0</v>
-      </c>
-      <c r="J44" s="98">
-        <v>0</v>
-      </c>
-      <c r="K44" s="98">
-        <v>0</v>
-      </c>
-      <c r="L44" s="98">
-        <v>0</v>
-      </c>
-      <c r="M44" s="98">
-        <v>0</v>
-      </c>
-      <c r="N44" s="98">
-        <v>0</v>
-      </c>
-      <c r="O44" s="98">
+      <c r="B44" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="104">
+        <v>0</v>
+      </c>
+      <c r="D44" s="104">
+        <v>0</v>
+      </c>
+      <c r="E44" s="104">
+        <v>0</v>
+      </c>
+      <c r="F44" s="104">
+        <v>0</v>
+      </c>
+      <c r="G44" s="104">
+        <v>0</v>
+      </c>
+      <c r="H44" s="104">
+        <v>0</v>
+      </c>
+      <c r="I44" s="104">
+        <v>1000</v>
+      </c>
+      <c r="J44" s="104">
+        <v>0</v>
+      </c>
+      <c r="K44" s="104">
+        <v>0</v>
+      </c>
+      <c r="L44" s="104">
+        <v>0</v>
+      </c>
+      <c r="M44" s="104">
+        <v>0</v>
+      </c>
+      <c r="N44" s="104">
+        <v>0</v>
+      </c>
+      <c r="O44" s="104">
         <v>0</v>
       </c>
       <c r="P44" s="72">
-        <f>SUM(C44:O44)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1000</v>
       </c>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="A45" s="96" t="s">
-        <v>31</v>
-      </c>
-      <c r="B45" s="97"/>
-      <c r="C45" s="98">
-        <v>0</v>
-      </c>
-      <c r="D45" s="98">
-        <v>0</v>
-      </c>
-      <c r="E45" s="98">
-        <v>0</v>
-      </c>
-      <c r="F45" s="98">
-        <v>0</v>
-      </c>
-      <c r="G45" s="98">
-        <v>0</v>
-      </c>
-      <c r="H45" s="98">
-        <v>0</v>
-      </c>
-      <c r="I45" s="98">
-        <v>0</v>
-      </c>
-      <c r="J45" s="98">
-        <v>0</v>
-      </c>
-      <c r="K45" s="98">
-        <v>0</v>
-      </c>
-      <c r="L45" s="98">
-        <v>0</v>
-      </c>
-      <c r="M45" s="98">
-        <v>0</v>
-      </c>
-      <c r="N45" s="98">
-        <v>0</v>
-      </c>
-      <c r="O45" s="98">
+      <c r="A45" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="103"/>
+      <c r="C45" s="104">
+        <v>0</v>
+      </c>
+      <c r="D45" s="104">
+        <v>0</v>
+      </c>
+      <c r="E45" s="104">
+        <v>0</v>
+      </c>
+      <c r="F45" s="104">
+        <v>0</v>
+      </c>
+      <c r="G45" s="104">
+        <v>0</v>
+      </c>
+      <c r="H45" s="104">
+        <v>0</v>
+      </c>
+      <c r="I45" s="104">
+        <v>0</v>
+      </c>
+      <c r="J45" s="104">
+        <v>0</v>
+      </c>
+      <c r="K45" s="104">
+        <v>0</v>
+      </c>
+      <c r="L45" s="104">
+        <v>0</v>
+      </c>
+      <c r="M45" s="104">
+        <v>0</v>
+      </c>
+      <c r="N45" s="104">
+        <v>0</v>
+      </c>
+      <c r="O45" s="104">
         <v>0</v>
       </c>
       <c r="P45" s="72">
-        <f>SUM(C45:O45)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="A46" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="97"/>
-      <c r="C46" s="98">
-        <v>0</v>
-      </c>
-      <c r="D46" s="98">
-        <v>0</v>
-      </c>
-      <c r="E46" s="98">
-        <v>0</v>
-      </c>
-      <c r="F46" s="98">
-        <v>0</v>
-      </c>
-      <c r="G46" s="98">
-        <v>0</v>
-      </c>
-      <c r="H46" s="98">
-        <v>0</v>
-      </c>
-      <c r="I46" s="98">
-        <v>0</v>
-      </c>
-      <c r="J46" s="98">
-        <v>0</v>
-      </c>
-      <c r="K46" s="98">
-        <v>0</v>
-      </c>
-      <c r="L46" s="98">
-        <v>0</v>
-      </c>
-      <c r="M46" s="98">
-        <v>0</v>
-      </c>
-      <c r="N46" s="98">
-        <v>0</v>
-      </c>
-      <c r="O46" s="98">
+      <c r="A46" s="102" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="103"/>
+      <c r="C46" s="104">
+        <v>0</v>
+      </c>
+      <c r="D46" s="104">
+        <v>0</v>
+      </c>
+      <c r="E46" s="104">
+        <v>0</v>
+      </c>
+      <c r="F46" s="104">
+        <v>0</v>
+      </c>
+      <c r="G46" s="104">
+        <v>0</v>
+      </c>
+      <c r="H46" s="104">
+        <v>0</v>
+      </c>
+      <c r="I46" s="104">
+        <v>0</v>
+      </c>
+      <c r="J46" s="104">
+        <v>0</v>
+      </c>
+      <c r="K46" s="104">
+        <v>0</v>
+      </c>
+      <c r="L46" s="104">
+        <v>0</v>
+      </c>
+      <c r="M46" s="104">
+        <v>0</v>
+      </c>
+      <c r="N46" s="104">
+        <v>0</v>
+      </c>
+      <c r="O46" s="104">
         <v>0</v>
       </c>
       <c r="P46" s="72">
-        <f>SUM(C46:O46)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="A47" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="97"/>
-      <c r="C47" s="98">
-        <v>0</v>
-      </c>
-      <c r="D47" s="98">
-        <v>0</v>
-      </c>
-      <c r="E47" s="98">
-        <v>0</v>
-      </c>
-      <c r="F47" s="98">
-        <v>0</v>
-      </c>
-      <c r="G47" s="98">
-        <v>0</v>
-      </c>
-      <c r="H47" s="98">
-        <v>0</v>
-      </c>
-      <c r="I47" s="98">
-        <v>0</v>
-      </c>
-      <c r="J47" s="98">
-        <v>0</v>
-      </c>
-      <c r="K47" s="98">
-        <v>0</v>
-      </c>
-      <c r="L47" s="98">
-        <v>0</v>
-      </c>
-      <c r="M47" s="98">
-        <v>0</v>
-      </c>
-      <c r="N47" s="98">
-        <v>0</v>
-      </c>
-      <c r="O47" s="98">
+      <c r="A47" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="103"/>
+      <c r="C47" s="104">
+        <v>0</v>
+      </c>
+      <c r="D47" s="104">
+        <v>0</v>
+      </c>
+      <c r="E47" s="104">
+        <v>0</v>
+      </c>
+      <c r="F47" s="104">
+        <v>0</v>
+      </c>
+      <c r="G47" s="104">
+        <v>0</v>
+      </c>
+      <c r="H47" s="104">
+        <v>0</v>
+      </c>
+      <c r="I47" s="104">
+        <v>0</v>
+      </c>
+      <c r="J47" s="104">
+        <v>0</v>
+      </c>
+      <c r="K47" s="104">
+        <v>0</v>
+      </c>
+      <c r="L47" s="104">
+        <v>0</v>
+      </c>
+      <c r="M47" s="104">
+        <v>0</v>
+      </c>
+      <c r="N47" s="104">
+        <v>0</v>
+      </c>
+      <c r="O47" s="104">
         <v>0</v>
       </c>
       <c r="P47" s="72">
-        <f>SUM(C47:O47)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="A48" s="96" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="97"/>
-      <c r="C48" s="98">
-        <v>0</v>
-      </c>
-      <c r="D48" s="98">
-        <v>0</v>
-      </c>
-      <c r="E48" s="98">
-        <v>0</v>
-      </c>
-      <c r="F48" s="98">
-        <v>0</v>
-      </c>
-      <c r="G48" s="98">
-        <v>0</v>
-      </c>
-      <c r="H48" s="98">
-        <v>0</v>
-      </c>
-      <c r="I48" s="98">
-        <v>0</v>
-      </c>
-      <c r="J48" s="98">
-        <v>0</v>
-      </c>
-      <c r="K48" s="98">
-        <v>0</v>
-      </c>
-      <c r="L48" s="98">
-        <v>0</v>
-      </c>
-      <c r="M48" s="98">
-        <v>0</v>
-      </c>
-      <c r="N48" s="98">
-        <v>0</v>
-      </c>
-      <c r="O48" s="98">
+      <c r="A48" s="102" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="103"/>
+      <c r="C48" s="104">
+        <v>0</v>
+      </c>
+      <c r="D48" s="104">
+        <v>0</v>
+      </c>
+      <c r="E48" s="104">
+        <v>0</v>
+      </c>
+      <c r="F48" s="104">
+        <v>0</v>
+      </c>
+      <c r="G48" s="104">
+        <v>0</v>
+      </c>
+      <c r="H48" s="104">
+        <v>0</v>
+      </c>
+      <c r="I48" s="104">
+        <v>0</v>
+      </c>
+      <c r="J48" s="104">
+        <v>0</v>
+      </c>
+      <c r="K48" s="104">
+        <v>0</v>
+      </c>
+      <c r="L48" s="104">
+        <v>0</v>
+      </c>
+      <c r="M48" s="104">
+        <v>0</v>
+      </c>
+      <c r="N48" s="104">
+        <v>0</v>
+      </c>
+      <c r="O48" s="104">
         <v>0</v>
       </c>
       <c r="P48" s="72">
-        <f>SUM(C48:O48)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="A49" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="97"/>
-      <c r="C49" s="98">
+      <c r="A49" s="102" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="103"/>
+      <c r="C49" s="104">
         <v>200</v>
       </c>
-      <c r="D49" s="98">
-        <v>0</v>
-      </c>
-      <c r="E49" s="98">
-        <v>0</v>
-      </c>
-      <c r="F49" s="98">
-        <v>0</v>
-      </c>
-      <c r="G49" s="98">
-        <v>0</v>
-      </c>
-      <c r="H49" s="98">
-        <v>0</v>
-      </c>
-      <c r="I49" s="98">
-        <v>0</v>
-      </c>
-      <c r="J49" s="98">
-        <v>0</v>
-      </c>
-      <c r="K49" s="98">
-        <v>0</v>
-      </c>
-      <c r="L49" s="98">
-        <v>0</v>
-      </c>
-      <c r="M49" s="98">
-        <v>0</v>
-      </c>
-      <c r="N49" s="98">
-        <v>0</v>
-      </c>
-      <c r="O49" s="98">
+      <c r="D49" s="104">
+        <v>0</v>
+      </c>
+      <c r="E49" s="104">
+        <v>0</v>
+      </c>
+      <c r="F49" s="104">
+        <v>0</v>
+      </c>
+      <c r="G49" s="104">
+        <v>0</v>
+      </c>
+      <c r="H49" s="104">
+        <v>0</v>
+      </c>
+      <c r="I49" s="104">
+        <v>0</v>
+      </c>
+      <c r="J49" s="104">
+        <v>0</v>
+      </c>
+      <c r="K49" s="104">
+        <v>0</v>
+      </c>
+      <c r="L49" s="104">
+        <v>0</v>
+      </c>
+      <c r="M49" s="104">
+        <v>0</v>
+      </c>
+      <c r="N49" s="104">
+        <v>0</v>
+      </c>
+      <c r="O49" s="104">
         <v>0</v>
       </c>
       <c r="P49" s="72">
-        <f>SUM(C49:O49)</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
     </row>
     <row r="50" ht="12" customHeight="1">
-      <c r="A50" s="96" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="97"/>
-      <c r="C50" s="98">
-        <v>0</v>
-      </c>
-      <c r="D50" s="98">
-        <v>0</v>
-      </c>
-      <c r="E50" s="98">
-        <v>0</v>
-      </c>
-      <c r="F50" s="98">
-        <v>0</v>
-      </c>
-      <c r="G50" s="98">
-        <v>0</v>
-      </c>
-      <c r="H50" s="98">
-        <v>0</v>
-      </c>
-      <c r="I50" s="98">
-        <v>0</v>
-      </c>
-      <c r="J50" s="98">
-        <v>0</v>
-      </c>
-      <c r="K50" s="98">
-        <v>0</v>
-      </c>
-      <c r="L50" s="98">
-        <v>0</v>
-      </c>
-      <c r="M50" s="98">
-        <v>0</v>
-      </c>
-      <c r="N50" s="98">
-        <v>0</v>
-      </c>
-      <c r="O50" s="98">
+      <c r="A50" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="103"/>
+      <c r="C50" s="104">
+        <v>0</v>
+      </c>
+      <c r="D50" s="104">
+        <v>0</v>
+      </c>
+      <c r="E50" s="104">
+        <v>0</v>
+      </c>
+      <c r="F50" s="104">
+        <v>0</v>
+      </c>
+      <c r="G50" s="104">
+        <v>0</v>
+      </c>
+      <c r="H50" s="104">
+        <v>0</v>
+      </c>
+      <c r="I50" s="104">
+        <v>0</v>
+      </c>
+      <c r="J50" s="104">
+        <v>0</v>
+      </c>
+      <c r="K50" s="104">
+        <v>0</v>
+      </c>
+      <c r="L50" s="104">
+        <v>0</v>
+      </c>
+      <c r="M50" s="104">
+        <v>0</v>
+      </c>
+      <c r="N50" s="104">
+        <v>0</v>
+      </c>
+      <c r="O50" s="104">
         <v>0</v>
       </c>
       <c r="P50" s="72">
-        <f>SUM(C50:O50)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" ht="12" customHeight="1">
-      <c r="A51" s="96" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="97"/>
-      <c r="C51" s="98">
+      <c r="A51" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="103"/>
+      <c r="C51" s="104">
         <v>300</v>
       </c>
-      <c r="D51" s="98">
-        <v>0</v>
-      </c>
-      <c r="E51" s="98">
-        <v>0</v>
-      </c>
-      <c r="F51" s="98">
-        <v>0</v>
-      </c>
-      <c r="G51" s="98">
-        <v>0</v>
-      </c>
-      <c r="H51" s="98">
-        <v>0</v>
-      </c>
-      <c r="I51" s="98">
-        <v>0</v>
-      </c>
-      <c r="J51" s="98">
-        <v>0</v>
-      </c>
-      <c r="K51" s="98">
-        <v>0</v>
-      </c>
-      <c r="L51" s="98">
-        <v>0</v>
-      </c>
-      <c r="M51" s="98">
-        <v>0</v>
-      </c>
-      <c r="N51" s="98">
-        <v>0</v>
-      </c>
-      <c r="O51" s="98">
+      <c r="D51" s="104">
+        <v>0</v>
+      </c>
+      <c r="E51" s="104">
+        <v>0</v>
+      </c>
+      <c r="F51" s="104">
+        <v>0</v>
+      </c>
+      <c r="G51" s="104">
+        <v>0</v>
+      </c>
+      <c r="H51" s="104">
+        <v>0</v>
+      </c>
+      <c r="I51" s="104">
+        <v>0</v>
+      </c>
+      <c r="J51" s="104">
+        <v>0</v>
+      </c>
+      <c r="K51" s="104">
+        <v>0</v>
+      </c>
+      <c r="L51" s="104">
+        <v>0</v>
+      </c>
+      <c r="M51" s="104">
+        <v>0</v>
+      </c>
+      <c r="N51" s="104">
+        <v>0</v>
+      </c>
+      <c r="O51" s="104">
         <v>0</v>
       </c>
       <c r="P51" s="72">
-        <f>SUM(C51:O51)</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
-    <row r="52" ht="12" customHeight="1">
-      <c r="A52" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="97"/>
-      <c r="C52" s="98">
-        <v>0</v>
-      </c>
-      <c r="D52" s="98">
-        <v>0</v>
-      </c>
-      <c r="E52" s="98">
-        <v>0</v>
-      </c>
-      <c r="F52" s="98">
-        <v>0</v>
-      </c>
-      <c r="G52" s="98">
-        <v>0</v>
-      </c>
-      <c r="H52" s="98">
-        <v>0</v>
-      </c>
-      <c r="I52" s="98">
-        <v>0</v>
-      </c>
-      <c r="J52" s="98">
-        <v>0</v>
-      </c>
-      <c r="K52" s="98">
-        <v>0</v>
-      </c>
-      <c r="L52" s="98">
-        <v>0</v>
-      </c>
-      <c r="M52" s="98">
-        <v>0</v>
-      </c>
-      <c r="N52" s="98">
-        <v>0</v>
-      </c>
-      <c r="O52" s="98">
+    <row r="52" ht="25.5" customHeight="1">
+      <c r="A52" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="103"/>
+      <c r="C52" s="104">
+        <v>0</v>
+      </c>
+      <c r="D52" s="104">
+        <v>0</v>
+      </c>
+      <c r="E52" s="104">
+        <v>0</v>
+      </c>
+      <c r="F52" s="104">
+        <v>0</v>
+      </c>
+      <c r="G52" s="104">
+        <v>0</v>
+      </c>
+      <c r="H52" s="104">
+        <v>0</v>
+      </c>
+      <c r="I52" s="104">
+        <v>0</v>
+      </c>
+      <c r="J52" s="104">
+        <v>0</v>
+      </c>
+      <c r="K52" s="104">
+        <v>0</v>
+      </c>
+      <c r="L52" s="104">
+        <v>0</v>
+      </c>
+      <c r="M52" s="104">
+        <v>0</v>
+      </c>
+      <c r="N52" s="104">
+        <v>0</v>
+      </c>
+      <c r="O52" s="104">
         <v>0</v>
       </c>
       <c r="P52" s="72">
-        <f>SUM(C52:O52)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="97"/>
-      <c r="C53" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="103"/>
+      <c r="C53" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="99" t="e">
+      <c r="D53" s="105" t="e">
         <f>IF(#REF!&lt;0,-#REF!,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="E53" s="99" t="e">
+      <c r="E53" s="105" t="e">
         <f>D53</f>
         <v>#REF!</v>
       </c>
-      <c r="F53" s="99" t="e">
+      <c r="F53" s="105" t="e">
         <f>E53</f>
         <v>#REF!</v>
       </c>
-      <c r="G53" s="99" t="e">
+      <c r="G53" s="105" t="e">
         <f>F53</f>
         <v>#REF!</v>
       </c>
-      <c r="H53" s="99" t="e">
+      <c r="H53" s="105" t="e">
         <f>G53</f>
         <v>#REF!</v>
       </c>
-      <c r="I53" s="99" t="e">
+      <c r="I53" s="105" t="e">
         <f>H53</f>
         <v>#REF!</v>
       </c>
-      <c r="J53" s="99" t="e">
+      <c r="J53" s="105" t="e">
         <f>I53</f>
         <v>#REF!</v>
       </c>
-      <c r="K53" s="99" t="e">
+      <c r="K53" s="105" t="e">
         <f>J53</f>
         <v>#REF!</v>
       </c>
-      <c r="L53" s="99" t="e">
+      <c r="L53" s="105" t="e">
         <f>K53</f>
         <v>#REF!</v>
       </c>
-      <c r="M53" s="99" t="e">
+      <c r="M53" s="105" t="e">
         <f>L53</f>
         <v>#REF!</v>
       </c>
-      <c r="N53" s="99" t="e">
+      <c r="N53" s="105" t="e">
         <f>M53</f>
         <v>#REF!</v>
       </c>
-      <c r="O53" s="99" t="e">
+      <c r="O53" s="105" t="e">
         <f>N53</f>
         <v>#REF!</v>
       </c>
@@ -6028,591 +6077,601 @@
     </row>
     <row r="54" ht="14.25">
       <c r="A54" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="97"/>
-      <c r="C54" s="98" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="103"/>
+      <c r="C54" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="98">
-        <v>0</v>
-      </c>
-      <c r="E54" s="98">
-        <v>0</v>
-      </c>
-      <c r="F54" s="98">
-        <v>0</v>
-      </c>
-      <c r="G54" s="98">
-        <v>0</v>
-      </c>
-      <c r="H54" s="98">
-        <v>0</v>
-      </c>
-      <c r="I54" s="98">
-        <v>0</v>
-      </c>
-      <c r="J54" s="98">
-        <v>0</v>
-      </c>
-      <c r="K54" s="98">
-        <v>0</v>
-      </c>
-      <c r="L54" s="98">
-        <v>0</v>
-      </c>
-      <c r="M54" s="98">
-        <v>0</v>
-      </c>
-      <c r="N54" s="98">
-        <v>0</v>
-      </c>
-      <c r="O54" s="98">
+      <c r="D54" s="104">
+        <v>0</v>
+      </c>
+      <c r="E54" s="104">
+        <v>0</v>
+      </c>
+      <c r="F54" s="104">
+        <v>0</v>
+      </c>
+      <c r="G54" s="104">
+        <v>0</v>
+      </c>
+      <c r="H54" s="104">
+        <v>0</v>
+      </c>
+      <c r="I54" s="104">
+        <v>0</v>
+      </c>
+      <c r="J54" s="104">
+        <v>0</v>
+      </c>
+      <c r="K54" s="104">
+        <v>0</v>
+      </c>
+      <c r="L54" s="104">
+        <v>0</v>
+      </c>
+      <c r="M54" s="104">
+        <v>0</v>
+      </c>
+      <c r="N54" s="104">
+        <v>0</v>
+      </c>
+      <c r="O54" s="104">
         <v>0</v>
       </c>
       <c r="P54" s="72">
-        <f>SUM(C54:O54)</f>
+        <f t="shared" ref="P54:P63" si="1">SUM(C54:O54)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="97"/>
-      <c r="C55" s="98">
-        <v>0</v>
-      </c>
-      <c r="D55" s="98">
+      <c r="A55" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="103"/>
+      <c r="C55" s="104">
+        <v>1000</v>
+      </c>
+      <c r="D55" s="104">
         <v>250</v>
       </c>
-      <c r="E55" s="98">
+      <c r="E55" s="104">
         <v>250</v>
       </c>
-      <c r="F55" s="98">
+      <c r="F55" s="104">
         <v>250</v>
       </c>
-      <c r="G55" s="98">
+      <c r="G55" s="104">
         <v>250</v>
       </c>
-      <c r="H55" s="98">
+      <c r="H55" s="104">
         <v>250</v>
       </c>
-      <c r="I55" s="98">
+      <c r="I55" s="104">
+        <v>750</v>
+      </c>
+      <c r="J55" s="104">
         <v>250</v>
       </c>
-      <c r="J55" s="98">
-        <v>0</v>
-      </c>
-      <c r="K55" s="98">
-        <v>0</v>
-      </c>
-      <c r="L55" s="98">
-        <v>0</v>
-      </c>
-      <c r="M55" s="98">
-        <v>0</v>
-      </c>
-      <c r="N55" s="98">
-        <v>0</v>
-      </c>
-      <c r="O55" s="98">
+      <c r="K55" s="104">
+        <v>250</v>
+      </c>
+      <c r="L55" s="104">
+        <v>0</v>
+      </c>
+      <c r="M55" s="104">
+        <v>0</v>
+      </c>
+      <c r="N55" s="104">
+        <v>0</v>
+      </c>
+      <c r="O55" s="104">
         <v>0</v>
       </c>
       <c r="P55" s="72">
         <f>SUM(C55:O55)</f>
-        <v>1500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="56" ht="14.25">
       <c r="A56" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="97"/>
-      <c r="C56" s="98" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="103"/>
+      <c r="C56" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="100" t="str">
+      <c r="D56" s="107" t="str">
         <f>B19</f>
         <v/>
       </c>
-      <c r="E56" s="99" t="str">
+      <c r="E56" s="105" t="str">
         <f>D56</f>
         <v/>
       </c>
-      <c r="F56" s="99" t="str">
+      <c r="F56" s="105" t="str">
         <f>E56</f>
         <v/>
       </c>
-      <c r="G56" s="99" t="str">
+      <c r="G56" s="105" t="str">
         <f>F56</f>
         <v/>
       </c>
-      <c r="H56" s="99" t="str">
+      <c r="H56" s="105" t="str">
         <f>G56</f>
         <v/>
       </c>
-      <c r="I56" s="99" t="str">
+      <c r="I56" s="105" t="str">
         <f>H56</f>
         <v/>
       </c>
-      <c r="J56" s="99" t="str">
+      <c r="J56" s="105" t="str">
         <f>I56</f>
         <v/>
       </c>
-      <c r="K56" s="99" t="str">
+      <c r="K56" s="105" t="str">
         <f>J56</f>
         <v/>
       </c>
-      <c r="L56" s="99" t="str">
+      <c r="L56" s="105" t="str">
         <f>K56</f>
         <v/>
       </c>
-      <c r="M56" s="99" t="str">
+      <c r="M56" s="105" t="str">
         <f>L56</f>
         <v/>
       </c>
-      <c r="N56" s="99" t="str">
+      <c r="N56" s="105" t="str">
         <f>M56</f>
         <v/>
       </c>
-      <c r="O56" s="99" t="str">
+      <c r="O56" s="105" t="str">
         <f>N56</f>
         <v/>
       </c>
       <c r="P56" s="72">
-        <f>SUM(C56:O56)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" ht="14.25">
       <c r="A57" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="97"/>
-      <c r="C57" s="98">
+        <v>44</v>
+      </c>
+      <c r="B57" s="106" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="104">
         <v>900</v>
       </c>
-      <c r="D57" s="98">
+      <c r="D57" s="104">
         <v>50</v>
       </c>
-      <c r="E57" s="98">
+      <c r="E57" s="104">
         <v>50</v>
       </c>
-      <c r="F57" s="98">
+      <c r="F57" s="104">
         <v>50</v>
       </c>
-      <c r="G57" s="98">
+      <c r="G57" s="104">
         <v>50</v>
       </c>
-      <c r="H57" s="98">
+      <c r="H57" s="104">
         <v>50</v>
       </c>
-      <c r="I57" s="98">
+      <c r="I57" s="104">
         <v>50</v>
       </c>
-      <c r="J57" s="98">
+      <c r="J57" s="104">
         <v>50</v>
       </c>
-      <c r="K57" s="98">
+      <c r="K57" s="104">
         <v>50</v>
       </c>
-      <c r="L57" s="98">
+      <c r="L57" s="104">
         <v>50</v>
       </c>
-      <c r="M57" s="98">
+      <c r="M57" s="104">
         <v>50</v>
       </c>
-      <c r="N57" s="98">
-        <v>0</v>
-      </c>
-      <c r="O57" s="98">
+      <c r="N57" s="104">
+        <v>0</v>
+      </c>
+      <c r="O57" s="104">
         <v>0</v>
       </c>
       <c r="P57" s="72">
-        <f>SUM(C57:O57)</f>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
     </row>
     <row r="58" ht="14.25">
       <c r="A58" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="97"/>
-      <c r="C58" s="98">
+        <v>46</v>
+      </c>
+      <c r="B58" s="106" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="104">
         <v>250</v>
       </c>
-      <c r="D58" s="98">
+      <c r="D58" s="104">
         <v>50</v>
       </c>
-      <c r="E58" s="98">
+      <c r="E58" s="104">
         <v>50</v>
       </c>
-      <c r="F58" s="98">
+      <c r="F58" s="104">
         <v>50</v>
       </c>
-      <c r="G58" s="98">
+      <c r="G58" s="104">
         <v>50</v>
       </c>
-      <c r="H58" s="98">
+      <c r="H58" s="104">
         <v>50</v>
       </c>
-      <c r="I58" s="98">
+      <c r="I58" s="104">
         <v>50</v>
       </c>
-      <c r="J58" s="98">
+      <c r="J58" s="104">
         <v>50</v>
       </c>
-      <c r="K58" s="98">
+      <c r="K58" s="104">
         <v>50</v>
       </c>
-      <c r="L58" s="98">
+      <c r="L58" s="104">
         <v>50</v>
       </c>
-      <c r="M58" s="98">
+      <c r="M58" s="104">
         <v>50</v>
       </c>
-      <c r="N58" s="98">
-        <v>0</v>
-      </c>
-      <c r="O58" s="98">
+      <c r="N58" s="104">
+        <v>0</v>
+      </c>
+      <c r="O58" s="104">
         <v>0</v>
       </c>
       <c r="P58" s="72">
-        <f>SUM(C58:O58)</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="A59" s="73" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="97"/>
-      <c r="C59" s="98">
+        <v>48</v>
+      </c>
+      <c r="B59" s="106" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="104">
         <v>200</v>
       </c>
-      <c r="D59" s="98">
-        <v>0</v>
-      </c>
-      <c r="E59" s="98">
-        <v>0</v>
-      </c>
-      <c r="F59" s="98">
-        <v>0</v>
-      </c>
-      <c r="G59" s="98">
-        <v>0</v>
-      </c>
-      <c r="H59" s="98">
-        <v>0</v>
-      </c>
-      <c r="I59" s="98">
-        <v>0</v>
-      </c>
-      <c r="J59" s="98">
-        <v>0</v>
-      </c>
-      <c r="K59" s="98">
-        <v>0</v>
-      </c>
-      <c r="L59" s="98">
-        <v>0</v>
-      </c>
-      <c r="M59" s="98">
-        <v>0</v>
-      </c>
-      <c r="N59" s="98">
-        <v>0</v>
-      </c>
-      <c r="O59" s="98">
+      <c r="D59" s="104">
+        <v>0</v>
+      </c>
+      <c r="E59" s="104">
+        <v>0</v>
+      </c>
+      <c r="F59" s="104">
+        <v>0</v>
+      </c>
+      <c r="G59" s="104">
+        <v>0</v>
+      </c>
+      <c r="H59" s="104">
+        <v>0</v>
+      </c>
+      <c r="I59" s="104">
+        <v>0</v>
+      </c>
+      <c r="J59" s="104">
+        <v>0</v>
+      </c>
+      <c r="K59" s="104">
+        <v>0</v>
+      </c>
+      <c r="L59" s="104">
+        <v>0</v>
+      </c>
+      <c r="M59" s="104">
+        <v>0</v>
+      </c>
+      <c r="N59" s="104">
+        <v>0</v>
+      </c>
+      <c r="O59" s="104">
         <v>0</v>
       </c>
       <c r="P59" s="72">
-        <f>SUM(C59:O59)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="A60" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="97"/>
-      <c r="C60" s="98">
+        <v>50</v>
+      </c>
+      <c r="B60" s="106"/>
+      <c r="C60" s="104">
         <v>250</v>
       </c>
-      <c r="D60" s="98">
-        <v>0</v>
-      </c>
-      <c r="E60" s="98">
-        <v>0</v>
-      </c>
-      <c r="F60" s="98">
-        <v>0</v>
-      </c>
-      <c r="G60" s="98">
-        <v>0</v>
-      </c>
-      <c r="H60" s="98">
-        <v>0</v>
-      </c>
-      <c r="I60" s="98">
-        <v>0</v>
-      </c>
-      <c r="J60" s="98">
-        <v>0</v>
-      </c>
-      <c r="K60" s="98">
-        <v>0</v>
-      </c>
-      <c r="L60" s="98">
-        <v>0</v>
-      </c>
-      <c r="M60" s="98">
-        <v>0</v>
-      </c>
-      <c r="N60" s="98">
-        <v>0</v>
-      </c>
-      <c r="O60" s="98">
+      <c r="D60" s="104">
+        <v>0</v>
+      </c>
+      <c r="E60" s="104">
+        <v>0</v>
+      </c>
+      <c r="F60" s="104">
+        <v>0</v>
+      </c>
+      <c r="G60" s="104">
+        <v>0</v>
+      </c>
+      <c r="H60" s="104">
+        <v>0</v>
+      </c>
+      <c r="I60" s="104">
+        <v>0</v>
+      </c>
+      <c r="J60" s="104">
+        <v>0</v>
+      </c>
+      <c r="K60" s="104">
+        <v>0</v>
+      </c>
+      <c r="L60" s="104">
+        <v>0</v>
+      </c>
+      <c r="M60" s="104">
+        <v>0</v>
+      </c>
+      <c r="N60" s="104">
+        <v>0</v>
+      </c>
+      <c r="O60" s="104">
         <v>0</v>
       </c>
       <c r="P60" s="72">
-        <f>SUM(C60:O60)</f>
+        <f t="shared" si="1"/>
         <v>250</v>
       </c>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="B61" s="97"/>
-      <c r="C61" s="98">
+        <v>51</v>
+      </c>
+      <c r="B61" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="104">
         <v>200</v>
       </c>
-      <c r="D61" s="98">
-        <v>0</v>
-      </c>
-      <c r="E61" s="98">
-        <v>0</v>
-      </c>
-      <c r="F61" s="98">
-        <v>0</v>
-      </c>
-      <c r="G61" s="98">
-        <v>0</v>
-      </c>
-      <c r="H61" s="98">
-        <v>0</v>
-      </c>
-      <c r="I61" s="98">
-        <v>0</v>
-      </c>
-      <c r="J61" s="98">
-        <v>0</v>
-      </c>
-      <c r="K61" s="98">
-        <v>0</v>
-      </c>
-      <c r="L61" s="98">
-        <v>0</v>
-      </c>
-      <c r="M61" s="98">
-        <v>0</v>
-      </c>
-      <c r="N61" s="98">
-        <v>0</v>
-      </c>
-      <c r="O61" s="98">
+      <c r="D61" s="104">
+        <v>0</v>
+      </c>
+      <c r="E61" s="104">
+        <v>0</v>
+      </c>
+      <c r="F61" s="104">
+        <v>0</v>
+      </c>
+      <c r="G61" s="104">
+        <v>0</v>
+      </c>
+      <c r="H61" s="104">
+        <v>0</v>
+      </c>
+      <c r="I61" s="104">
+        <v>0</v>
+      </c>
+      <c r="J61" s="104">
+        <v>0</v>
+      </c>
+      <c r="K61" s="104">
+        <v>0</v>
+      </c>
+      <c r="L61" s="104">
+        <v>0</v>
+      </c>
+      <c r="M61" s="104">
+        <v>0</v>
+      </c>
+      <c r="N61" s="104">
+        <v>0</v>
+      </c>
+      <c r="O61" s="104">
         <v>0</v>
       </c>
       <c r="P61" s="72">
-        <f>SUM(C61:O61)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="102"/>
-      <c r="C62" s="103">
+      <c r="A62" s="108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="109" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="110">
         <v>200</v>
       </c>
-      <c r="D62" s="103">
-        <v>0</v>
-      </c>
-      <c r="E62" s="103">
-        <v>0</v>
-      </c>
-      <c r="F62" s="103">
-        <v>0</v>
-      </c>
-      <c r="G62" s="103">
-        <v>0</v>
-      </c>
-      <c r="H62" s="103">
-        <v>0</v>
-      </c>
-      <c r="I62" s="103">
-        <v>0</v>
-      </c>
-      <c r="J62" s="103">
-        <v>0</v>
-      </c>
-      <c r="K62" s="103">
-        <v>0</v>
-      </c>
-      <c r="L62" s="103">
-        <v>0</v>
-      </c>
-      <c r="M62" s="103">
-        <v>0</v>
-      </c>
-      <c r="N62" s="103">
-        <v>0</v>
-      </c>
-      <c r="O62" s="103">
+      <c r="D62" s="110">
+        <v>0</v>
+      </c>
+      <c r="E62" s="110">
+        <v>0</v>
+      </c>
+      <c r="F62" s="110">
+        <v>0</v>
+      </c>
+      <c r="G62" s="110">
+        <v>0</v>
+      </c>
+      <c r="H62" s="110">
+        <v>0</v>
+      </c>
+      <c r="I62" s="110">
+        <v>0</v>
+      </c>
+      <c r="J62" s="110">
+        <v>0</v>
+      </c>
+      <c r="K62" s="110">
+        <v>0</v>
+      </c>
+      <c r="L62" s="110">
+        <v>0</v>
+      </c>
+      <c r="M62" s="110">
+        <v>0</v>
+      </c>
+      <c r="N62" s="110">
+        <v>0</v>
+      </c>
+      <c r="O62" s="110">
         <v>0</v>
       </c>
       <c r="P62" s="77">
-        <f>SUM(C62:O62)</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="104" t="s">
-        <v>49</v>
-      </c>
-      <c r="B63" s="105"/>
-      <c r="C63" s="106">
+      <c r="A63" s="111" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="112"/>
+      <c r="C63" s="113">
         <f>SUM(C40:C62)</f>
-        <v>2500</v>
-      </c>
-      <c r="D63" s="106" t="e">
+        <v>3500</v>
+      </c>
+      <c r="D63" s="113" t="e">
         <f>SUM(D40:D62)</f>
         <v>#REF!</v>
       </c>
-      <c r="E63" s="106" t="e">
+      <c r="E63" s="113" t="e">
         <f>SUM(E40:E62)</f>
         <v>#REF!</v>
       </c>
-      <c r="F63" s="106" t="e">
+      <c r="F63" s="113" t="e">
         <f>SUM(F40:F62)</f>
         <v>#REF!</v>
       </c>
-      <c r="G63" s="106" t="e">
+      <c r="G63" s="113" t="e">
         <f>SUM(G40:G62)</f>
         <v>#REF!</v>
       </c>
-      <c r="H63" s="106" t="e">
+      <c r="H63" s="113" t="e">
         <f>SUM(H40:H62)</f>
         <v>#REF!</v>
       </c>
-      <c r="I63" s="107" t="e">
+      <c r="I63" s="114" t="e">
         <f>SUM(I40:I62)</f>
         <v>#REF!</v>
       </c>
-      <c r="J63" s="108" t="e">
+      <c r="J63" s="115" t="e">
         <f>SUM(J40:J62)</f>
         <v>#REF!</v>
       </c>
-      <c r="K63" s="108" t="e">
+      <c r="K63" s="115" t="e">
         <f>SUM(K40:K62)</f>
         <v>#REF!</v>
       </c>
-      <c r="L63" s="108" t="e">
+      <c r="L63" s="115" t="e">
         <f>SUM(L40:L62)</f>
         <v>#REF!</v>
       </c>
-      <c r="M63" s="108" t="e">
+      <c r="M63" s="115" t="e">
         <f>SUM(M40:M62)</f>
         <v>#REF!</v>
       </c>
-      <c r="N63" s="108" t="e">
+      <c r="N63" s="115" t="e">
         <f>SUM(N40:N62)</f>
         <v>#REF!</v>
       </c>
-      <c r="O63" s="108" t="e">
+      <c r="O63" s="115" t="e">
         <f>SUM(O40:O62)</f>
         <v>#REF!</v>
       </c>
-      <c r="P63" s="109" t="e">
-        <f>SUM(C63:O63)</f>
+      <c r="P63" s="116" t="e">
+        <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
     </row>
     <row r="64" ht="14.25">
       <c r="A64" s="17"/>
-      <c r="B64" s="110"/>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="111"/>
-      <c r="F64" s="111"/>
-      <c r="G64" s="111"/>
-      <c r="H64" s="111"/>
-      <c r="I64" s="111"/>
-      <c r="J64" s="111"/>
-      <c r="K64" s="111"/>
-      <c r="L64" s="111"/>
-      <c r="M64" s="111"/>
-      <c r="N64" s="111"/>
-      <c r="O64" s="111"/>
-      <c r="P64" s="112"/>
+      <c r="B64" s="117"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="118"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="118"/>
+      <c r="G64" s="118"/>
+      <c r="H64" s="118"/>
+      <c r="I64" s="118"/>
+      <c r="J64" s="118"/>
+      <c r="K64" s="118"/>
+      <c r="L64" s="118"/>
+      <c r="M64" s="118"/>
+      <c r="N64" s="118"/>
+      <c r="O64" s="118"/>
+      <c r="P64" s="119"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="113"/>
-      <c r="B65" s="114" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" s="115">
+      <c r="A65" s="120"/>
+      <c r="B65" s="121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="122">
         <f>C35-C63</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="106" t="e">
+        <v>1000</v>
+      </c>
+      <c r="D65" s="113" t="e">
         <f>D35-D63</f>
         <v>#REF!</v>
       </c>
-      <c r="E65" s="106" t="e">
+      <c r="E65" s="113" t="e">
         <f>E35-E63</f>
         <v>#REF!</v>
       </c>
-      <c r="F65" s="106" t="e">
+      <c r="F65" s="113" t="e">
         <f>F35-F63</f>
         <v>#REF!</v>
       </c>
-      <c r="G65" s="106" t="e">
+      <c r="G65" s="113" t="e">
         <f>G35-G63</f>
         <v>#REF!</v>
       </c>
-      <c r="H65" s="106" t="e">
+      <c r="H65" s="113" t="e">
         <f>H35-H63</f>
         <v>#REF!</v>
       </c>
-      <c r="I65" s="106" t="e">
+      <c r="I65" s="113" t="e">
         <f>I35-I63</f>
         <v>#REF!</v>
       </c>
-      <c r="J65" s="106" t="e">
+      <c r="J65" s="113" t="e">
         <f>J35-J63</f>
         <v>#REF!</v>
       </c>
-      <c r="K65" s="106" t="e">
+      <c r="K65" s="113" t="e">
         <f>K35-K63</f>
         <v>#REF!</v>
       </c>
-      <c r="L65" s="106" t="e">
+      <c r="L65" s="113" t="e">
         <f>L35-L63</f>
         <v>#REF!</v>
       </c>
-      <c r="M65" s="106" t="e">
+      <c r="M65" s="113" t="e">
         <f>M35-M63</f>
         <v>#REF!</v>
       </c>
-      <c r="N65" s="106" t="e">
+      <c r="N65" s="113" t="e">
         <f>N35-N63</f>
         <v>#REF!</v>
       </c>
-      <c r="O65" s="106" t="e">
+      <c r="O65" s="113" t="e">
         <f>O35-O63</f>
         <v>#REF!</v>
       </c>
@@ -6623,75 +6682,75 @@
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="17"/>
-      <c r="B66" s="116"/>
-      <c r="C66" s="117"/>
-      <c r="D66" s="117"/>
-      <c r="E66" s="117"/>
-      <c r="F66" s="117"/>
-      <c r="G66" s="117"/>
-      <c r="H66" s="117"/>
-      <c r="I66" s="117"/>
-      <c r="J66" s="117"/>
-      <c r="K66" s="117"/>
-      <c r="L66" s="117"/>
-      <c r="M66" s="117"/>
-      <c r="N66" s="117"/>
-      <c r="O66" s="117"/>
-      <c r="P66" s="117"/>
+      <c r="B66" s="123"/>
+      <c r="C66" s="124"/>
+      <c r="D66" s="124"/>
+      <c r="E66" s="124"/>
+      <c r="F66" s="124"/>
+      <c r="G66" s="124"/>
+      <c r="H66" s="124"/>
+      <c r="I66" s="124"/>
+      <c r="J66" s="124"/>
+      <c r="K66" s="124"/>
+      <c r="L66" s="124"/>
+      <c r="M66" s="124"/>
+      <c r="N66" s="124"/>
+      <c r="O66" s="124"/>
+      <c r="P66" s="124"/>
     </row>
     <row r="67" ht="60.75" customHeight="1">
-      <c r="A67" s="118"/>
-      <c r="B67" s="119" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="120">
-        <v>0</v>
-      </c>
-      <c r="D67" s="106">
+      <c r="A67" s="125"/>
+      <c r="B67" s="126" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="127">
+        <v>0</v>
+      </c>
+      <c r="D67" s="113">
         <f>C69</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="106" t="e">
+        <v>1000</v>
+      </c>
+      <c r="E67" s="113" t="e">
         <f>D69</f>
         <v>#REF!</v>
       </c>
-      <c r="F67" s="106" t="e">
+      <c r="F67" s="113" t="e">
         <f>E69</f>
         <v>#REF!</v>
       </c>
-      <c r="G67" s="106" t="e">
+      <c r="G67" s="113" t="e">
         <f>F69</f>
         <v>#REF!</v>
       </c>
-      <c r="H67" s="106" t="e">
+      <c r="H67" s="113" t="e">
         <f>G69</f>
         <v>#REF!</v>
       </c>
-      <c r="I67" s="106" t="e">
+      <c r="I67" s="113" t="e">
         <f>H69</f>
         <v>#REF!</v>
       </c>
-      <c r="J67" s="106" t="e">
+      <c r="J67" s="113" t="e">
         <f>I69</f>
         <v>#REF!</v>
       </c>
-      <c r="K67" s="106" t="e">
+      <c r="K67" s="113" t="e">
         <f>J69</f>
         <v>#REF!</v>
       </c>
-      <c r="L67" s="106" t="e">
+      <c r="L67" s="113" t="e">
         <f>K69</f>
         <v>#REF!</v>
       </c>
-      <c r="M67" s="106" t="e">
+      <c r="M67" s="113" t="e">
         <f>L69</f>
         <v>#REF!</v>
       </c>
-      <c r="N67" s="106" t="e">
+      <c r="N67" s="113" t="e">
         <f>M69</f>
         <v>#REF!</v>
       </c>
-      <c r="O67" s="106" t="e">
+      <c r="O67" s="113" t="e">
         <f>N69</f>
         <v>#REF!</v>
       </c>
@@ -6701,77 +6760,77 @@
       </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="121"/>
-      <c r="B68" s="122"/>
-      <c r="C68" s="117"/>
-      <c r="D68" s="117"/>
-      <c r="E68" s="117"/>
-      <c r="F68" s="117"/>
-      <c r="G68" s="117"/>
-      <c r="H68" s="117"/>
-      <c r="I68" s="117"/>
-      <c r="J68" s="117"/>
-      <c r="K68" s="117"/>
-      <c r="L68" s="117"/>
-      <c r="M68" s="117"/>
-      <c r="N68" s="117"/>
-      <c r="O68" s="117"/>
-      <c r="P68" s="117"/>
+      <c r="A68" s="128"/>
+      <c r="B68" s="129"/>
+      <c r="C68" s="124"/>
+      <c r="D68" s="124"/>
+      <c r="E68" s="124"/>
+      <c r="F68" s="124"/>
+      <c r="G68" s="124"/>
+      <c r="H68" s="124"/>
+      <c r="I68" s="124"/>
+      <c r="J68" s="124"/>
+      <c r="K68" s="124"/>
+      <c r="L68" s="124"/>
+      <c r="M68" s="124"/>
+      <c r="N68" s="124"/>
+      <c r="O68" s="124"/>
+      <c r="P68" s="124"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="118"/>
-      <c r="B69" s="119" t="s">
-        <v>52</v>
-      </c>
-      <c r="C69" s="115">
+      <c r="A69" s="125"/>
+      <c r="B69" s="126" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="122">
         <f>C65+C67</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="106" t="e">
+        <v>1000</v>
+      </c>
+      <c r="D69" s="113" t="e">
         <f>D65+D67</f>
         <v>#REF!</v>
       </c>
-      <c r="E69" s="106" t="e">
+      <c r="E69" s="113" t="e">
         <f>E65+E67</f>
         <v>#REF!</v>
       </c>
-      <c r="F69" s="106" t="e">
+      <c r="F69" s="113" t="e">
         <f>F65+F67</f>
         <v>#REF!</v>
       </c>
-      <c r="G69" s="106" t="e">
+      <c r="G69" s="113" t="e">
         <f>G65+G67</f>
         <v>#REF!</v>
       </c>
-      <c r="H69" s="106" t="e">
+      <c r="H69" s="113" t="e">
         <f>H65+H67</f>
         <v>#REF!</v>
       </c>
-      <c r="I69" s="106" t="e">
+      <c r="I69" s="113" t="e">
         <f>I65+I67</f>
         <v>#REF!</v>
       </c>
-      <c r="J69" s="106" t="e">
+      <c r="J69" s="113" t="e">
         <f>J65+J67</f>
         <v>#REF!</v>
       </c>
-      <c r="K69" s="106" t="e">
+      <c r="K69" s="113" t="e">
         <f>K65+K67</f>
         <v>#REF!</v>
       </c>
-      <c r="L69" s="106" t="e">
+      <c r="L69" s="113" t="e">
         <f>L65+L67</f>
         <v>#REF!</v>
       </c>
-      <c r="M69" s="106" t="e">
+      <c r="M69" s="113" t="e">
         <f>M65+M67</f>
         <v>#REF!</v>
       </c>
-      <c r="N69" s="106" t="e">
+      <c r="N69" s="113" t="e">
         <f>N65+N67</f>
         <v>#REF!</v>
       </c>
-      <c r="O69" s="106" t="e">
+      <c r="O69" s="113" t="e">
         <f>O65+O67</f>
         <v>#REF!</v>
       </c>
@@ -6800,10 +6859,10 @@
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="17"/>
-      <c r="B71" s="123" t="s">
-        <v>53</v>
-      </c>
-      <c r="C71" s="124" t="e">
+      <c r="B71" s="130" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71" s="131" t="e">
         <f t="array" ref="C71">_xlfn.IFS(#REF!="Stress test at 10% reduction in revenue",0.9,#REF!="Stress test at 15% reduction in revenue",0.85,#REF!="Stress test at 20% reduction in revenue",0.8)</f>
         <v>#REF!</v>
       </c>
@@ -6823,8 +6882,8 @@
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="17"/>
-      <c r="B72" s="123" t="s">
-        <v>54</v>
+      <c r="B72" s="130" t="s">
+        <v>60</v>
       </c>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
@@ -6843,8 +6902,8 @@
     </row>
     <row r="73" ht="14.25">
       <c r="A73" s="17"/>
-      <c r="B73" s="123" t="s">
-        <v>55</v>
+      <c r="B73" s="130" t="s">
+        <v>61</v>
       </c>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
@@ -6898,58 +6957,58 @@
       <c r="P75" s="17"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="125"/>
-      <c r="B76" s="126" t="s">
-        <v>56</v>
-      </c>
-      <c r="C76" s="127"/>
-      <c r="D76" s="127"/>
-      <c r="E76" s="127"/>
-      <c r="F76" s="127"/>
-      <c r="G76" s="127"/>
-      <c r="H76" s="127"/>
-      <c r="I76" s="127"/>
-      <c r="J76" s="127"/>
-      <c r="K76" s="127"/>
-      <c r="L76" s="128"/>
+      <c r="A76" s="132"/>
+      <c r="B76" s="133" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="134"/>
+      <c r="J76" s="134"/>
+      <c r="K76" s="134"/>
+      <c r="L76" s="135"/>
       <c r="M76" s="17"/>
       <c r="N76" s="17"/>
       <c r="O76" s="17"/>
       <c r="P76" s="17"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="125"/>
-      <c r="B77" s="129" t="s">
-        <v>57</v>
-      </c>
-      <c r="C77" s="130"/>
-      <c r="D77" s="130"/>
-      <c r="E77" s="130"/>
-      <c r="F77" s="130"/>
-      <c r="G77" s="130"/>
-      <c r="H77" s="130"/>
-      <c r="I77" s="130"/>
-      <c r="J77" s="130"/>
-      <c r="K77" s="130"/>
-      <c r="L77" s="131"/>
+      <c r="A77" s="132"/>
+      <c r="B77" s="136" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="137"/>
+      <c r="D77" s="137"/>
+      <c r="E77" s="137"/>
+      <c r="F77" s="137"/>
+      <c r="G77" s="137"/>
+      <c r="H77" s="137"/>
+      <c r="I77" s="137"/>
+      <c r="J77" s="137"/>
+      <c r="K77" s="137"/>
+      <c r="L77" s="138"/>
       <c r="M77" s="17"/>
       <c r="N77" s="17"/>
       <c r="O77" s="17"/>
       <c r="P77" s="17"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="125"/>
-      <c r="B78" s="132"/>
-      <c r="C78" s="133"/>
-      <c r="D78" s="133"/>
-      <c r="E78" s="133"/>
-      <c r="F78" s="133"/>
-      <c r="G78" s="133"/>
-      <c r="H78" s="133"/>
-      <c r="I78" s="133"/>
-      <c r="J78" s="133"/>
-      <c r="K78" s="133"/>
-      <c r="L78" s="134"/>
+      <c r="A78" s="132"/>
+      <c r="B78" s="139"/>
+      <c r="C78" s="140"/>
+      <c r="D78" s="140"/>
+      <c r="E78" s="140"/>
+      <c r="F78" s="140"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="140"/>
+      <c r="I78" s="140"/>
+      <c r="J78" s="140"/>
+      <c r="K78" s="140"/>
+      <c r="L78" s="141"/>
       <c r="M78" s="17"/>
       <c r="N78" s="17"/>
       <c r="O78" s="17"/>
@@ -6982,7 +7041,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00330002-0015-4DEC-8408-00AD004B0091}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{001E004E-00FA-4399-891D-00BC00E2005C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$B$89:$B$100</xm:f>
           </x14:formula1>
